--- a/outputs/week2_excel/301563_云汉芯城_三表抽取.xlsx
+++ b/outputs/week2_excel/301563_云汉芯城_三表抽取.xlsx
@@ -2419,13 +2419,13 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>张松满</t>
+          <t>孙国奉</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>162.5</t>
+          <t>175.0</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
@@ -2499,13 +2499,13 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>孙国奉</t>
+          <t>张松满</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>175.0</t>
+          <t>162.5</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
@@ -2537,7 +2537,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>东方富海（上海）创业投资企业（有限合伙）</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
@@ -2575,7 +2575,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
+          <t>东方富海（上海）创业投资企业（有限合伙）</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
@@ -2735,7 +2735,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
@@ -2773,7 +2773,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>深圳市创新投资集团有限公司</t>
+          <t>镇江红土创业投资有限公司</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
+          <t>昆山红土高新创业投资有限公司</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
@@ -2849,7 +2849,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>深圳市创新投资集团有限公司</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
@@ -2865,7 +2865,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2925,7 +2925,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>镇江红土创业投资有限公司</t>
+          <t>丰利财富（北京）国际资本管理股份有限公司</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>昆山红土高新创业投资有限公司</t>
+          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
@@ -2979,7 +2979,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>丰利财富（北京）国际资本管理股份有限公司</t>
+          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
@@ -3039,15 +3039,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>丰利财富（北京）国际资本管理股份有限公司</t>
+          <t>曾烨</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
@@ -3059,7 +3055,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3081,7 +3077,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>曾烨</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
@@ -3195,11 +3191,15 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>深圳市创新投资集团有限公司</t>
+          <t>丰利财富（北京）国际资本管理股份有限公司</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
@@ -3233,7 +3233,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>刘云锋</t>
+          <t>深圳市创新投资集团有限公司</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
@@ -3249,7 +3249,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3271,7 +3271,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
+          <t>刘云锋</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3309,7 +3309,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
@@ -3325,7 +3325,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3347,7 +3347,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
+          <t>曾烨</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
@@ -3363,7 +3363,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3385,7 +3385,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>CASREV FUND</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
@@ -3401,7 +3401,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3423,7 +3423,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>珠海拓域投资合伙企业（有限合伙）</t>
+          <t>夏东</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
@@ -3499,7 +3499,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>曾烨</t>
+          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
@@ -3515,7 +3515,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3537,7 +3537,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
+          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
@@ -3575,7 +3575,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
@@ -3591,7 +3591,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3613,7 +3613,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>夏东</t>
+          <t>CASREV FUND</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
@@ -3651,7 +3651,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
+          <t>珠海拓域投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
@@ -3689,13 +3689,13 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
+          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>1584.0</t>
+          <t>7412.0</t>
         </is>
       </c>
       <c r="G58" t="inlineStr"/>
@@ -3731,13 +3731,13 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>CASREV FUND</t>
+          <t>珠海拓域投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>1000.0</t>
         </is>
       </c>
       <c r="G59" t="inlineStr"/>
@@ -3773,13 +3773,13 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>夏东</t>
+          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>1584.0</t>
         </is>
       </c>
       <c r="G60" t="inlineStr"/>
@@ -3815,15 +3815,11 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>珠海拓域投资合伙企业（有限合伙）</t>
+          <t>火炬电子科技股份有限公司</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
@@ -3835,7 +3831,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3857,11 +3853,15 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>火炬电子科技股份有限公司</t>
+          <t>CASREV FUND</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr"/>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3895,13 +3895,13 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
+          <t>夏东</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
-          <t>7412.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="G63" t="inlineStr"/>
@@ -3979,15 +3979,11 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>火炬电子科技股份有限公司</t>
+          <t>中小企业发展基金（深圳有限合伙）</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>5000.0</t>
-        </is>
-      </c>
+      <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
@@ -3999,7 +3995,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4021,11 +4017,15 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>中小企业发展基金（深圳有限合伙）</t>
+          <t>火炬电子科技股份有限公司</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr"/>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>5000.0</t>
+        </is>
+      </c>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
@@ -4037,7 +4037,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4097,7 +4097,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>张俊武</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
@@ -4135,15 +4135,11 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>昆山谷捷金属制品有限公司</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr"/>
@@ -4155,7 +4151,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4177,7 +4173,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>张俊武</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
@@ -4215,11 +4211,15 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>昆山谷捷金属制品有限公司</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr"/>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr"/>
@@ -4231,7 +4231,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>上海广弘实业有限公司</t>
+          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
@@ -4469,7 +4469,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
+          <t>上海广弘实业有限公司</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
@@ -4587,11 +4587,15 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>黄山佳捷股权管理中心（有限合伙）</t>
+          <t>上海广弘实业有限公司</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr"/>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>10377.0</t>
+        </is>
+      </c>
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr"/>
@@ -4603,7 +4607,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4625,15 +4629,11 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>上海广弘实业有限公司</t>
+          <t>黄山佳捷股权管理中心（有限合伙）</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>10377.0</t>
-        </is>
-      </c>
+      <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr"/>
@@ -4645,7 +4645,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4667,7 +4667,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>张俊武</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
@@ -4705,7 +4705,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>张俊武</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
@@ -4743,7 +4743,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>上海广弘实业有限公司</t>
+          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
         </is>
       </c>
       <c r="E85" t="inlineStr"/>
@@ -4781,7 +4781,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
+          <t>上海广弘实业有限公司</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
@@ -4857,7 +4857,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
@@ -5545,14 +5545,22 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>上海市青浦县徐泾乡工业公司</t>
+          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr"/>
-      <c r="G102" t="inlineStr"/>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>1020.0</t>
+        </is>
+      </c>
       <c r="H102" t="inlineStr"/>
-      <c r="I102" t="inlineStr"/>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>1020.0</t>
+        </is>
+      </c>
       <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr">
         <is>
@@ -5561,7 +5569,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5629,22 +5637,14 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>罗世兵</t>
+          <t>友升太平洋(美国)投资有限公司</t>
         </is>
       </c>
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr"/>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>204.0</t>
-        </is>
-      </c>
+      <c r="G104" t="inlineStr"/>
       <c r="H104" t="inlineStr"/>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>204.0</t>
-        </is>
-      </c>
+      <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr">
         <is>
@@ -5653,7 +5653,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5675,14 +5675,22 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>友升太平洋(美国)投资有限公司</t>
+          <t>上海泽升贸易有限公司</t>
         </is>
       </c>
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr"/>
-      <c r="G105" t="inlineStr"/>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>8976.0</t>
+        </is>
+      </c>
       <c r="H105" t="inlineStr"/>
-      <c r="I105" t="inlineStr"/>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>8976.0</t>
+        </is>
+      </c>
       <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr">
         <is>
@@ -5691,7 +5699,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5713,22 +5721,14 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>上海泽升贸易有限公司</t>
+          <t>上海市青浦县徐泾乡工业公司</t>
         </is>
       </c>
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr"/>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>8976.0</t>
-        </is>
-      </c>
+      <c r="G106" t="inlineStr"/>
       <c r="H106" t="inlineStr"/>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>8976.0</t>
-        </is>
-      </c>
+      <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr">
         <is>
@@ -5737,7 +5737,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5759,20 +5759,20 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
+          <t>罗世兵</t>
         </is>
       </c>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr">
         <is>
-          <t>1020.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="H107" t="inlineStr"/>
       <c r="I107" t="inlineStr">
         <is>
-          <t>1020.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="J107" t="inlineStr"/>
@@ -5805,23 +5805,23 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
+          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>1020.0</t>
         </is>
       </c>
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>1020.0</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>3600.0</t>
+          <t>2040.0</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -5855,22 +5855,26 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr"/>
+          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr">
         <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr"/>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
+          <t>1800.0</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>3600.0</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr">
         <is>
@@ -5879,7 +5883,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5901,26 +5905,22 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>罗世兵</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>204.0</t>
-        </is>
-      </c>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr">
         <is>
-          <t>204.0</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>408.0</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr"/>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr">
         <is>
@@ -5929,7 +5929,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5951,22 +5951,26 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>上海骁墨信息技术服务中心(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr"/>
+          <t>上海泽升贸易有限公司</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>8976.0</t>
+        </is>
+      </c>
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
         <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr"/>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
+          <t>8976.0</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>17952.0</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr">
         <is>
@@ -5975,7 +5979,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5997,20 +6001,20 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+          <t>上海骁墨信息技术服务中心(有限合伙)</t>
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr">
         <is>
-          <t>840.0</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="H112" t="inlineStr"/>
       <c r="I112" t="inlineStr">
         <is>
-          <t>840.0</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="J112" t="inlineStr"/>
@@ -6043,23 +6047,23 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>上海泽升贸易有限公司</t>
+          <t>罗世兵</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>8976.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
-          <t>8976.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>17952.0</t>
+          <t>408.0</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -6093,26 +6097,22 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>1020.0</t>
-        </is>
-      </c>
+          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr">
         <is>
-          <t>1020.0</t>
-        </is>
-      </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>2040.0</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr"/>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
       <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr">
         <is>
@@ -6121,7 +6121,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6143,22 +6143,30 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>深圳市达晨创程私募股权投资基金企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr"/>
-      <c r="F115" t="inlineStr"/>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>7000.0</t>
+        </is>
+      </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>86.5984</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr"/>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>86.5984</t>
-        </is>
-      </c>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>1680.0</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr">
         <is>
@@ -6167,7 +6175,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -6189,20 +6197,20 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>上海联炻企业管理中心(有限合伙)</t>
+          <t>江西赣江新区财投晨源股权投资中心(有限合伙)</t>
         </is>
       </c>
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="H116" t="inlineStr"/>
       <c r="I116" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="J116" t="inlineStr"/>
@@ -6281,20 +6289,20 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙)</t>
+          <t>上海联炻企业管理中心(有限合伙)</t>
         </is>
       </c>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="H118" t="inlineStr"/>
       <c r="I118" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="J118" t="inlineStr"/>
@@ -6327,22 +6335,30 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>深圳市财智创赢私募股权投资企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr"/>
-      <c r="F119" t="inlineStr"/>
+          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>3000.0</t>
+        </is>
+      </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>10.1093</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr"/>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>10.1093</t>
-        </is>
-      </c>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>720.0</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr">
         <is>
@@ -6351,7 +6367,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -6373,30 +6389,22 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>840.0</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>7000.0</t>
-        </is>
-      </c>
+          <t>深圳市达晨财智创业投资管理有限公司</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr"/>
+      <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr">
         <is>
-          <t>840.0</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>1680.0</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr"/>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr">
         <is>
@@ -6405,7 +6413,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6427,20 +6435,20 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>安吉璞颉企业管理合伙企业(有限合伙)</t>
+          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr">
         <is>
-          <t>148.6667</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="H121" t="inlineStr"/>
       <c r="I121" t="inlineStr">
         <is>
-          <t>148.6667</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="J121" t="inlineStr"/>
@@ -6473,27 +6481,27 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
+          <t>上海骁墨信息技术服务中心(有限合伙)</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>1500.0</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
           <t>360.0</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>3000.0</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>720.0</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -6527,20 +6535,20 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>上海杉创智至创业投资合伙企业(有限合伙)</t>
+          <t>深圳市杉晖创业投资合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr">
         <is>
-          <t>59.4667</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr">
         <is>
-          <t>59.4667</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="J123" t="inlineStr"/>
@@ -6573,20 +6581,20 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>深圳市达晨财智创业投资管理有限公司</t>
+          <t>深圳市达晨创程私募股权投资基金企业(有限合伙)</t>
         </is>
       </c>
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>86.5984</t>
         </is>
       </c>
       <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>86.5984</t>
         </is>
       </c>
       <c r="J124" t="inlineStr"/>
@@ -6619,20 +6627,20 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>江西赣江新区财投晨源股权投资中心(有限合伙)</t>
+          <t>上海杉创智至创业投资合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr"/>
       <c r="G125" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>59.4667</t>
         </is>
       </c>
       <c r="H125" t="inlineStr"/>
       <c r="I125" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>59.4667</t>
         </is>
       </c>
       <c r="J125" t="inlineStr"/>
@@ -6665,30 +6673,22 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>上海骁墨信息技术服务中心(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>1500.0</t>
-        </is>
-      </c>
+          <t>深圳市财智创赢私募股权投资企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr"/>
+      <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr">
         <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr"/>
+          <t>10.1093</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>10.1093</t>
+        </is>
+      </c>
       <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr">
         <is>
@@ -6697,7 +6697,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6719,20 +6719,20 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>深圳市杉晖创业投资合伙企业(有限合伙)</t>
+          <t>安吉璞颉企业管理合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr"/>
       <c r="G127" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>148.6667</t>
         </is>
       </c>
       <c r="H127" t="inlineStr"/>
       <c r="I127" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>148.6667</t>
         </is>
       </c>
       <c r="J127" t="inlineStr"/>
@@ -7615,7 +7615,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>华泰大健康一号</t>
+          <t>高新同华</t>
         </is>
       </c>
       <c r="E145" t="inlineStr"/>
@@ -7653,7 +7653,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>黄学英/刘鸿雁</t>
+          <t>黄学英</t>
         </is>
       </c>
       <c r="E146" t="inlineStr"/>
@@ -7669,7 +7669,7 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -7691,7 +7691,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>高新同华</t>
+          <t>周乃鼎</t>
         </is>
       </c>
       <c r="E147" t="inlineStr"/>
@@ -7707,7 +7707,7 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -7729,7 +7729,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>复星惟盈</t>
+          <t>陆民</t>
         </is>
       </c>
       <c r="E148" t="inlineStr"/>
@@ -7743,11 +7743,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L148" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
+      <c r="L148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -7767,7 +7763,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>黄学英</t>
+          <t>华泰大健康一号</t>
         </is>
       </c>
       <c r="E149" t="inlineStr"/>
@@ -7805,7 +7801,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>苏州贤达</t>
+          <t>复星惟盈</t>
         </is>
       </c>
       <c r="E150" t="inlineStr"/>
@@ -7843,7 +7839,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>周乃鼎</t>
+          <t>国寿疌泉</t>
         </is>
       </c>
       <c r="E151" t="inlineStr"/>
@@ -7859,7 +7855,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -7881,7 +7877,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>陆民</t>
+          <t>史建伟</t>
         </is>
       </c>
       <c r="E152" t="inlineStr"/>
@@ -7895,7 +7891,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L152" t="inlineStr"/>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -7915,7 +7915,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>史建伟</t>
+          <t>黄学英/刘鸿雁</t>
         </is>
       </c>
       <c r="E153" t="inlineStr"/>
@@ -7953,7 +7953,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Cheer Rise Consultants Limited</t>
+          <t>周金清</t>
         </is>
       </c>
       <c r="E154" t="inlineStr"/>
@@ -7969,7 +7969,7 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -7991,7 +7991,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>周金清</t>
+          <t>Cheer Rise Consultants Limited</t>
         </is>
       </c>
       <c r="E155" t="inlineStr"/>
@@ -8007,7 +8007,7 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -8029,7 +8029,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>国寿疌泉</t>
+          <t>苏州贤达</t>
         </is>
       </c>
       <c r="E156" t="inlineStr"/>
@@ -8105,7 +8105,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>深圳中证投资有限责任公司</t>
+          <t>QM101 Limited</t>
         </is>
       </c>
       <c r="E158" t="inlineStr"/>
@@ -8143,7 +8143,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>金石智娱股权投资（深圳）合伙企业（有限合伙）</t>
+          <t>华金同达（深圳）投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E159" t="inlineStr"/>
@@ -8219,7 +8219,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>香港迅雷有限公司</t>
         </is>
       </c>
       <c r="E161" t="inlineStr"/>
@@ -8235,7 +8235,7 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -8257,7 +8257,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>华金同达（深圳）投资合伙企业（有限合伙）</t>
+          <t>金石智娱股权投资（深圳）合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E162" t="inlineStr"/>
@@ -8295,7 +8295,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>厦门富凯海创投资管理有限责任公司</t>
+          <t>北京岚锋创视网络科技有限公司</t>
         </is>
       </c>
       <c r="E163" t="inlineStr"/>
@@ -8311,7 +8311,7 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -8333,7 +8333,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>深圳中证投资有限责任公司</t>
         </is>
       </c>
       <c r="E164" t="inlineStr"/>
@@ -8371,7 +8371,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>厦门富凯海创投资管理有限责任公司</t>
         </is>
       </c>
       <c r="E165" t="inlineStr"/>
@@ -8409,7 +8409,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>EARN ACE LIMITED</t>
         </is>
       </c>
       <c r="E166" t="inlineStr"/>
@@ -8447,7 +8447,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>QM101 Limited</t>
         </is>
       </c>
       <c r="E167" t="inlineStr"/>
@@ -8485,11 +8485,15 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>北京岚锋创视网络科技有限公司</t>
         </is>
       </c>
       <c r="E168" t="inlineStr"/>
-      <c r="F168" t="inlineStr"/>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G168" t="inlineStr"/>
       <c r="H168" t="inlineStr"/>
       <c r="I168" t="inlineStr"/>
@@ -8499,11 +8503,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L168" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
+      <c r="L168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -8523,15 +8523,11 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>香港迅雷有限公司</t>
         </is>
       </c>
       <c r="E169" t="inlineStr"/>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F169" t="inlineStr"/>
       <c r="G169" t="inlineStr"/>
       <c r="H169" t="inlineStr"/>
       <c r="I169" t="inlineStr"/>
@@ -8541,7 +8537,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L169" t="inlineStr"/>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -8561,7 +8561,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>EARN ACE LIMITED</t>
         </is>
       </c>
       <c r="E170" t="inlineStr"/>
@@ -8599,7 +8599,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>QM101 Limited</t>
         </is>
       </c>
       <c r="E171" t="inlineStr"/>
@@ -8675,7 +8675,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>北京岚锋创视网络科技有限公司</t>
         </is>
       </c>
       <c r="E173" t="inlineStr"/>
@@ -8713,7 +8713,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>香港迅雷有限公司</t>
         </is>
       </c>
       <c r="E174" t="inlineStr"/>
@@ -8915,15 +8915,11 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>吴功友(王金林代持)</t>
+          <t>牛威</t>
         </is>
       </c>
       <c r="E179" t="inlineStr"/>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>400.0</t>
-        </is>
-      </c>
+      <c r="F179" t="inlineStr"/>
       <c r="G179" t="inlineStr"/>
       <c r="H179" t="inlineStr"/>
       <c r="I179" t="inlineStr"/>
@@ -8935,7 +8931,7 @@
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -8957,7 +8953,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>牛威</t>
+          <t>吴功友</t>
         </is>
       </c>
       <c r="E180" t="inlineStr"/>
@@ -8995,13 +8991,13 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>四方股份</t>
+          <t>吴功友(王金林代持)</t>
         </is>
       </c>
       <c r="E181" t="inlineStr"/>
       <c r="F181" t="inlineStr">
         <is>
-          <t>1200.0</t>
+          <t>400.0</t>
         </is>
       </c>
       <c r="G181" t="inlineStr"/>
@@ -9037,11 +9033,15 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>吴功友</t>
+          <t>四方股份</t>
         </is>
       </c>
       <c r="E182" t="inlineStr"/>
-      <c r="F182" t="inlineStr"/>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>1200.0</t>
+        </is>
+      </c>
       <c r="G182" t="inlineStr"/>
       <c r="H182" t="inlineStr"/>
       <c r="I182" t="inlineStr"/>
@@ -9053,7 +9053,7 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -9117,20 +9117,20 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>策星揽月</t>
+          <t>幸福二期</t>
         </is>
       </c>
       <c r="E184" t="inlineStr"/>
       <c r="F184" t="inlineStr"/>
       <c r="G184" t="inlineStr">
         <is>
-          <t>412.5</t>
+          <t>300.0</t>
         </is>
       </c>
       <c r="H184" t="inlineStr"/>
       <c r="I184" t="inlineStr">
         <is>
-          <t>412.5</t>
+          <t>300.0</t>
         </is>
       </c>
       <c r="J184" t="inlineStr"/>
@@ -9205,20 +9205,20 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>中科星图股份有限公司</t>
+          <t>策星九天</t>
         </is>
       </c>
       <c r="E186" t="inlineStr"/>
       <c r="F186" t="inlineStr"/>
       <c r="G186" t="inlineStr">
         <is>
-          <t>3825.0</t>
+          <t>2345.0781</t>
         </is>
       </c>
       <c r="H186" t="inlineStr"/>
       <c r="I186" t="inlineStr">
         <is>
-          <t>3825.0</t>
+          <t>2345.0781</t>
         </is>
       </c>
       <c r="J186" t="inlineStr"/>
@@ -9251,20 +9251,20 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>策星九天</t>
+          <t>中科星图股份有限公司</t>
         </is>
       </c>
       <c r="E187" t="inlineStr"/>
       <c r="F187" t="inlineStr"/>
       <c r="G187" t="inlineStr">
         <is>
-          <t>2345.0781</t>
+          <t>3825.0</t>
         </is>
       </c>
       <c r="H187" t="inlineStr"/>
       <c r="I187" t="inlineStr">
         <is>
-          <t>2345.0781</t>
+          <t>3825.0</t>
         </is>
       </c>
       <c r="J187" t="inlineStr"/>
@@ -9339,20 +9339,20 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>幸福一期</t>
+          <t>策星揽月</t>
         </is>
       </c>
       <c r="E189" t="inlineStr"/>
       <c r="F189" t="inlineStr"/>
       <c r="G189" t="inlineStr">
         <is>
-          <t>917.4219</t>
+          <t>412.5</t>
         </is>
       </c>
       <c r="H189" t="inlineStr"/>
       <c r="I189" t="inlineStr">
         <is>
-          <t>917.4219</t>
+          <t>412.5</t>
         </is>
       </c>
       <c r="J189" t="inlineStr"/>
@@ -9385,20 +9385,20 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>策星银河</t>
+          <t>幸福一期</t>
         </is>
       </c>
       <c r="E190" t="inlineStr"/>
       <c r="F190" t="inlineStr"/>
       <c r="G190" t="inlineStr">
         <is>
-          <t>279.0</t>
+          <t>917.4219</t>
         </is>
       </c>
       <c r="H190" t="inlineStr"/>
       <c r="I190" t="inlineStr">
         <is>
-          <t>279.0</t>
+          <t>917.4219</t>
         </is>
       </c>
       <c r="J190" t="inlineStr"/>
@@ -9431,20 +9431,20 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>幸福二期</t>
+          <t>策星银河</t>
         </is>
       </c>
       <c r="E191" t="inlineStr"/>
       <c r="F191" t="inlineStr"/>
       <c r="G191" t="inlineStr">
         <is>
-          <t>300.0</t>
+          <t>279.0</t>
         </is>
       </c>
       <c r="H191" t="inlineStr"/>
       <c r="I191" t="inlineStr">
         <is>
-          <t>300.0</t>
+          <t>279.0</t>
         </is>
       </c>
       <c r="J191" t="inlineStr"/>
@@ -9872,7 +9872,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>生成时间: 2026-06-12T10:04:41.005746</t>
+          <t>生成时间: 2026-06-12T14:44:15.775996</t>
         </is>
       </c>
     </row>

--- a/outputs/week2_excel/301563_云汉芯城_三表抽取.xlsx
+++ b/outputs/week2_excel/301563_云汉芯城_三表抽取.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -452,7 +452,10 @@
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -488,6 +491,21 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>事件类型</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>增资后总股本(万股)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>认购占比</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>原文证据</t>
         </is>
       </c>
@@ -513,6 +531,16 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
+          <t>增资</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>50.00%</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>2008年4月17日，深圳市云汉电子有限公司和刘云锋共同申请设立上海云汉电子有限公司，注册资本50万元，深圳云汉电子认缴25万元（50%），刘云锋认缴25万元（50%）。2008年5月7日办理完毕工商登记。</t>
         </is>
       </c>
@@ -538,6 +566,16 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
+          <t>增资</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>50.00%</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>2008年4月17日，深圳市云汉电子有限公司和刘云锋共同申请设立上海云汉电子有限公司，注册资本50万元，深圳云汉电子认缴25万元（50%），刘云锋认缴25万元（50%）。2008年5月7日办理完毕工商登记。</t>
         </is>
       </c>
@@ -560,6 +598,11 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
+          <t>增资及股权转让</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>2009年12月，有限公司第一次股权转让及增资，注册资本增至100万元。深圳市云汉电子有限公司将其持有的有限公司50%股权转让给曾烨。曾烨、刘云锋按原持股比例增资50万元，注册资本增至100万元。</t>
         </is>
       </c>
@@ -582,6 +625,11 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
+          <t>增资及股权转让</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>2009年12月，有限公司第一次股权转让及增资，注册资本增至100万元。深圳市云汉电子有限公司将其持有的有限公司50%股权转让给曾烨。曾烨、刘云锋按原持股比例增资50万元，注册资本增至100万元。</t>
         </is>
       </c>
@@ -604,6 +652,16 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
+          <t>增资</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>10.25%</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>力源信息、东方富海及芜湖富海共同增资28.205万元，注册资本增至128.205万元。此轮引入了产业投资者力源信息（上市公司）及知名投资机构东方富海系。</t>
         </is>
       </c>
@@ -626,6 +684,16 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
+          <t>增资</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>5.12%</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>力源信息、东方富海及芜湖富海共同增资28.205万元，注册资本增至128.205万元。此轮引入了产业投资者力源信息（上市公司）及知名投资机构东方富海系。</t>
         </is>
       </c>
@@ -648,6 +716,16 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
+          <t>增资</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>5.81%</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>力源信息、东方富海及芜湖富海共同增资28.205万元，注册资本增至128.205万元。此轮引入了产业投资者力源信息（上市公司）及知名投资机构东方富海系。</t>
         </is>
       </c>
@@ -670,6 +748,16 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
+          <t>增资</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2.01%</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>深创投、丰利财富、镇江红土、昆山红土、富海深湾、芜湖富海共同增资158.2733万元，注册资本增至2,158.2733万元。丰利财富代表其管理的丰利新三板基金投资，投资总额1,000万元。B轮投资协议约定了2015年、2016年、2017-2018年业绩承诺及上市承诺。</t>
         </is>
       </c>
@@ -695,6 +783,16 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
+          <t>增资</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1.67%</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>深创投、丰利财富、镇江红土、昆山红土、富海深湾、芜湖富海共同增资158.2733万元，注册资本增至2,158.2733万元。丰利财富代表其管理的丰利新三板基金投资，投资总额1,000万元。B轮投资协议约定了2015年、2016年、2017-2018年业绩承诺及上市承诺。</t>
         </is>
       </c>
@@ -717,6 +815,16 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
+          <t>增资</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>0.72%</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>深创投、丰利财富、镇江红土、昆山红土、富海深湾、芜湖富海共同增资158.2733万元，注册资本增至2,158.2733万元。丰利财富代表其管理的丰利新三板基金投资，投资总额1,000万元。B轮投资协议约定了2015年、2016年、2017-2018年业绩承诺及上市承诺。</t>
         </is>
       </c>
@@ -739,6 +847,16 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
+          <t>增资</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>0.72%</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>深创投、丰利财富、镇江红土、昆山红土、富海深湾、芜湖富海共同增资158.2733万元，注册资本增至2,158.2733万元。丰利财富代表其管理的丰利新三板基金投资，投资总额1,000万元。B轮投资协议约定了2015年、2016年、2017-2018年业绩承诺及上市承诺。</t>
         </is>
       </c>
@@ -761,6 +879,16 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
+          <t>增资</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>0.72%</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
           <t>深创投、丰利财富、镇江红土、昆山红土、富海深湾、芜湖富海共同增资158.2733万元，注册资本增至2,158.2733万元。丰利财富代表其管理的丰利新三板基金投资，投资总额1,000万元。B轮投资协议约定了2015年、2016年、2017-2018年业绩承诺及上市承诺。</t>
         </is>
       </c>
@@ -783,6 +911,16 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>44.48%</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
           <t>2015年10月15日，全体发起人签署《发起人协议书》。有限公司将经审计净资产额45,010,412.64元按1.1253:1的比例折成4,000万股，每股面值1元，其余5,010,412.64元计入资本公积。2015年12月3日，上海市工商行政管理局核准。</t>
         </is>
       </c>
@@ -805,6 +943,16 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>18.53%</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
           <t>2015年10月15日，全体发起人签署《发起人协议书》。有限公司将经审计净资产额45,010,412.64元按1.1253:1的比例折成4,000万股，每股面值1元，其余5,010,412.64元计入资本公积。2015年12月3日，上海市工商行政管理局核准。</t>
         </is>
       </c>
@@ -827,6 +975,16 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>12.51%</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
           <t>2015年10月15日，全体发起人签署《发起人协议书》。有限公司将经审计净资产额45,010,412.64元按1.1253:1的比例折成4,000万股，每股面值1元，其余5,010,412.64元计入资本公积。2015年12月3日，上海市工商行政管理局核准。</t>
         </is>
       </c>
@@ -855,6 +1013,16 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
+          <t>增资及股权转让</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>5.49%</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
           <t>2018年6月12日，国科瑞华以现金7,412万元认缴新增注册资本254.4787万元；CASREV FUND以1,800万元等值美元认缴61.8万元；中科贵银以1,584万元认缴54.384万元；夏东以204万元认缴7.004万元；南山富海以3,000万元认缴103万元；珠海拓域以1,000万元认缴34.3333万元。每股价格约29.13元，对应投后估值约13.5亿元。注册资本增至4,635万元。</t>
         </is>
       </c>
@@ -883,6 +1051,16 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
+          <t>增资及股权转让</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1.33%</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
           <t>2018年6月12日，国科瑞华以现金7,412万元认缴新增注册资本254.4787万元；CASREV FUND以1,800万元等值美元认缴61.8万元；中科贵银以1,584万元认缴54.384万元；夏东以204万元认缴7.004万元；南山富海以3,000万元认缴103万元；珠海拓域以1,000万元认缴34.3333万元。每股价格约29.13元，对应投后估值约13.5亿元。注册资本增至4,635万元。</t>
         </is>
       </c>
@@ -911,6 +1089,16 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
+          <t>增资及股权转让</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1.17%</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
           <t>2018年6月12日，国科瑞华以现金7,412万元认缴新增注册资本254.4787万元；CASREV FUND以1,800万元等值美元认缴61.8万元；中科贵银以1,584万元认缴54.384万元；夏东以204万元认缴7.004万元；南山富海以3,000万元认缴103万元；珠海拓域以1,000万元认缴34.3333万元。每股价格约29.13元，对应投后估值约13.5亿元。注册资本增至4,635万元。</t>
         </is>
       </c>
@@ -939,6 +1127,16 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
+          <t>增资及股权转让</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2.22%</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
           <t>2018年6月12日，国科瑞华以现金7,412万元认缴新增注册资本254.4787万元；CASREV FUND以1,800万元等值美元认缴61.8万元；中科贵银以1,584万元认缴54.384万元；夏东以204万元认缴7.004万元；南山富海以3,000万元认缴103万元；珠海拓域以1,000万元认缴34.3333万元。每股价格约29.13元，对应投后估值约13.5亿元。注册资本增至4,635万元。</t>
         </is>
       </c>
@@ -967,6 +1165,16 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
+          <t>增资及股权转让</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>0.74%</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
           <t>2018年6月12日，国科瑞华以现金7,412万元认缴新增注册资本254.4787万元；CASREV FUND以1,800万元等值美元认缴61.8万元；中科贵银以1,584万元认缴54.384万元；夏东以204万元认缴7.004万元；南山富海以3,000万元认缴103万元；珠海拓域以1,000万元认缴34.3333万元。每股价格约29.13元，对应投后估值约13.5亿元。注册资本增至4,635万元。</t>
         </is>
       </c>
@@ -995,6 +1203,16 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
+          <t>增资及股权转让</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>0.15%</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
           <t>2018年6月12日，国科瑞华以现金7,412万元认缴新增注册资本254.4787万元；CASREV FUND以1,800万元等值美元认缴61.8万元；中科贵银以1,584万元认缴54.384万元；夏东以204万元认缴7.004万元；南山富海以3,000万元认缴103万元；珠海拓域以1,000万元认缴34.3333万元。每股价格约29.13元，对应投后估值约13.5亿元。注册资本增至4,635万元。</t>
         </is>
       </c>
@@ -1023,6 +1241,16 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
+          <t>增资</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2.38%</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
           <t>2020年5月20日召开临时股东大会，同意注册资本由4,635万元增至4,748.0488万元。火炬电子以现金5,000万元认购新增股份113.0488万股，每股价格约44.23元，对应投后估值约21亿元。</t>
         </is>
       </c>
@@ -1051,6 +1279,16 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
+          <t>增资及股权转让</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1.98%</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
           <t>2020年9月15日召开临时股东大会，同意注册资本由4,748.0488万元增至4,883.7074万元。厦门西堤以5,000万元认购96.899万股，中小企业基金以2,000万元认购38.7596万股。每股价格约51.6元，对应投后估值约25.2亿元。</t>
         </is>
       </c>
@@ -1078,6 +1316,16 @@
         <v>51.6</v>
       </c>
       <c r="G25" t="inlineStr">
+        <is>
+          <t>增资及股权转让</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>0.79%</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
         <is>
           <t>2020年9月15日召开临时股东大会，同意注册资本由4,748.0488万元增至4,883.7074万元。厦门西堤以5,000万元认购96.899万股，中小企业基金以2,000万元认购38.7596万股。每股价格约51.6元，对应投后估值约25.2亿元。</t>
         </is>
@@ -1094,7 +1342,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1106,7 +1354,10 @@
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="60" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1157,6 +1408,21 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>快照序号</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>股东类型</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>原始创始人</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>原文证据</t>
         </is>
       </c>
@@ -1192,6 +1458,21 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
+          <t>t1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
           <t>2008年4月17日，深圳市云汉电子有限公司和刘云锋共同申请设立上海云汉电子有限公司，注册资本50万元，深圳云汉电子认缴25万元（50%），刘云锋认缴25万元（50%）。2008年5月7日办理完毕工商登记。</t>
         </is>
       </c>
@@ -1227,6 +1508,21 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
+          <t>t1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>自然人</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
           <t>2008年4月17日，深圳市云汉电子有限公司和刘云锋共同申请设立上海云汉电子有限公司，注册资本50万元，深圳云汉电子认缴25万元（50%），刘云锋认缴25万元（50%）。2008年5月7日办理完毕工商登记。</t>
         </is>
       </c>
@@ -1259,6 +1555,21 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
+          <t>t2</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>产业资本</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
           <t>力源信息、东方富海及芜湖富海共同增资28.205万元，注册资本增至128.205万元。此轮引入了产业投资者力源信息（上市公司）及知名投资机构东方富海系。</t>
         </is>
       </c>
@@ -1291,6 +1602,21 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
+          <t>t2</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>外部PE</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
           <t>力源信息、东方富海及芜湖富海共同增资28.205万元，注册资本增至128.205万元。此轮引入了产业投资者力源信息（上市公司）及知名投资机构东方富海系。</t>
         </is>
       </c>
@@ -1323,6 +1649,21 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
+          <t>t2</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>外部PE</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
           <t>力源信息、东方富海及芜湖富海共同增资28.205万元，注册资本增至128.205万元。此轮引入了产业投资者力源信息（上市公司）及知名投资机构东方富海系。</t>
         </is>
       </c>
@@ -1355,6 +1696,21 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
+          <t>t3</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>外部PE</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
           <t>深创投、丰利财富、镇江红土、昆山红土、富海深湾、芜湖富海共同增资158.2733万元，注册资本增至2,158.2733万元。丰利财富代表其管理的丰利新三板基金投资，投资总额1,000万元。B轮投资协议约定了2015年、2016年、2017-2018年业绩承诺及上市承诺。</t>
         </is>
       </c>
@@ -1390,6 +1746,21 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
+          <t>t3</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>外部PE</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
           <t>深创投、丰利财富、镇江红土、昆山红土、富海深湾、芜湖富海共同增资158.2733万元，注册资本增至2,158.2733万元。丰利财富代表其管理的丰利新三板基金投资，投资总额1,000万元。B轮投资协议约定了2015年、2016年、2017-2018年业绩承诺及上市承诺。</t>
         </is>
       </c>
@@ -1422,6 +1793,21 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
+          <t>t3</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>外部PE</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
           <t>深创投、丰利财富、镇江红土、昆山红土、富海深湾、芜湖富海共同增资158.2733万元，注册资本增至2,158.2733万元。丰利财富代表其管理的丰利新三板基金投资，投资总额1,000万元。B轮投资协议约定了2015年、2016年、2017-2018年业绩承诺及上市承诺。</t>
         </is>
       </c>
@@ -1454,6 +1840,21 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
+          <t>t3</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>外部PE</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
           <t>深创投、丰利财富、镇江红土、昆山红土、富海深湾、芜湖富海共同增资158.2733万元，注册资本增至2,158.2733万元。丰利财富代表其管理的丰利新三板基金投资，投资总额1,000万元。B轮投资协议约定了2015年、2016年、2017-2018年业绩承诺及上市承诺。</t>
         </is>
       </c>
@@ -1486,6 +1887,21 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
+          <t>t3</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>外部PE</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
           <t>深创投、丰利财富、镇江红土、昆山红土、富海深湾、芜湖富海共同增资158.2733万元，注册资本增至2,158.2733万元。丰利财富代表其管理的丰利新三板基金投资，投资总额1,000万元。B轮投资协议约定了2015年、2016年、2017-2018年业绩承诺及上市承诺。</t>
         </is>
       </c>
@@ -1518,6 +1934,21 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
+          <t>t4</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>自然人</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
           <t>2015年10月15日，全体发起人签署《发起人协议书》。有限公司将经审计净资产额45,010,412.64元按1.1253:1的比例折成4,000万股，每股面值1元，其余5,010,412.64元计入资本公积。2015年12月3日，上海市工商行政管理局核准。</t>
         </is>
       </c>
@@ -1550,6 +1981,21 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
+          <t>t4</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>自然人</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
           <t>2015年10月15日，全体发起人签署《发起人协议书》。有限公司将经审计净资产额45,010,412.64元按1.1253:1的比例折成4,000万股，每股面值1元，其余5,010,412.64元计入资本公积。2015年12月3日，上海市工商行政管理局核准。</t>
         </is>
       </c>
@@ -1582,6 +2028,21 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
+          <t>t4</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>产业资本</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
           <t>2015年10月15日，全体发起人签署《发起人协议书》。有限公司将经审计净资产额45,010,412.64元按1.1253:1的比例折成4,000万股，每股面值1元，其余5,010,412.64元计入资本公积。2015年12月3日，上海市工商行政管理局核准。</t>
         </is>
       </c>
@@ -1620,6 +2081,21 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
+          <t>t5</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>外部PE</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
           <t>2018年6月12日，国科瑞华以现金7,412万元认缴新增注册资本254.4787万元；CASREV FUND以1,800万元等值美元认缴61.8万元；中科贵银以1,584万元认缴54.384万元；夏东以204万元认缴7.004万元；南山富海以3,000万元认缴103万元；珠海拓域以1,000万元认缴34.3333万元。每股价格约29.13元，对应投后估值约13.5亿元。注册资本增至4,635万元。</t>
         </is>
       </c>
@@ -1658,6 +2134,21 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
+          <t>t5</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>外部PE</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
           <t>2018年6月12日，国科瑞华以现金7,412万元认缴新增注册资本254.4787万元；CASREV FUND以1,800万元等值美元认缴61.8万元；中科贵银以1,584万元认缴54.384万元；夏东以204万元认缴7.004万元；南山富海以3,000万元认缴103万元；珠海拓域以1,000万元认缴34.3333万元。每股价格约29.13元，对应投后估值约13.5亿元。注册资本增至4,635万元。</t>
         </is>
       </c>
@@ -1696,6 +2187,21 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
+          <t>t5</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>外部PE</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
           <t>2018年6月12日，国科瑞华以现金7,412万元认缴新增注册资本254.4787万元；CASREV FUND以1,800万元等值美元认缴61.8万元；中科贵银以1,584万元认缴54.384万元；夏东以204万元认缴7.004万元；南山富海以3,000万元认缴103万元；珠海拓域以1,000万元认缴34.3333万元。每股价格约29.13元，对应投后估值约13.5亿元。注册资本增至4,635万元。</t>
         </is>
       </c>
@@ -1734,6 +2240,21 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
+          <t>t5</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>外部PE</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
           <t>2018年6月12日，国科瑞华以现金7,412万元认缴新增注册资本254.4787万元；CASREV FUND以1,800万元等值美元认缴61.8万元；中科贵银以1,584万元认缴54.384万元；夏东以204万元认缴7.004万元；南山富海以3,000万元认缴103万元；珠海拓域以1,000万元认缴34.3333万元。每股价格约29.13元，对应投后估值约13.5亿元。注册资本增至4,635万元。</t>
         </is>
       </c>
@@ -1772,6 +2293,21 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
+          <t>t5</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>外部PE</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
           <t>2018年6月12日，国科瑞华以现金7,412万元认缴新增注册资本254.4787万元；CASREV FUND以1,800万元等值美元认缴61.8万元；中科贵银以1,584万元认缴54.384万元；夏东以204万元认缴7.004万元；南山富海以3,000万元认缴103万元；珠海拓域以1,000万元认缴34.3333万元。每股价格约29.13元，对应投后估值约13.5亿元。注册资本增至4,635万元。</t>
         </is>
       </c>
@@ -1810,6 +2346,21 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
+          <t>t5</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>自然人</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
           <t>2018年6月12日，国科瑞华以现金7,412万元认缴新增注册资本254.4787万元；CASREV FUND以1,800万元等值美元认缴61.8万元；中科贵银以1,584万元认缴54.384万元；夏东以204万元认缴7.004万元；南山富海以3,000万元认缴103万元；珠海拓域以1,000万元认缴34.3333万元。每股价格约29.13元，对应投后估值约13.5亿元。注册资本增至4,635万元。</t>
         </is>
       </c>
@@ -1848,6 +2399,21 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
+          <t>t6</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>产业资本</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
           <t>2020年5月20日召开临时股东大会，同意注册资本由4,635万元增至4,748.0488万元。火炬电子以现金5,000万元认购新增股份113.0488万股，每股价格约44.23元，对应投后估值约21亿元。</t>
         </is>
       </c>
@@ -1886,6 +2452,21 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
+          <t>t7</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>外部PE</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
           <t>2020年9月15日召开临时股东大会，同意注册资本由4,748.0488万元增至4,883.7074万元。厦门西堤以5,000万元认购96.899万股，中小企业基金以2,000万元认购38.7596万股。每股价格约51.6元，对应投后估值约25.2亿元。</t>
         </is>
       </c>
@@ -1923,6 +2504,21 @@
         </is>
       </c>
       <c r="J23" t="inlineStr">
+        <is>
+          <t>t7</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>外部PE</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
         <is>
           <t>2020年9月15日召开临时股东大会，同意注册资本由4,748.0488万元增至4,883.7074万元。厦门西堤以5,000万元认购96.899万股，中小企业基金以2,000万元认购38.7596万股。每股价格约51.6元，对应投后估值约25.2亿元。</t>
         </is>
@@ -1939,7 +2535,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L203"/>
+  <dimension ref="A1:L211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2113,100 +2709,84 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>evidence_text</t>
+          <t>event_context</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>str(min=20)</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>equity_snapshot</t>
+          <t>subscription_flow</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>source_page</t>
+          <t>post_event_total_shares</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>str</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+          <t>float|null</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>equity_snapshot</t>
+          <t>subscription_flow</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>snapshot_date</t>
+          <t>post_event_total_capital</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>str(YYYY-MM-DD)</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+          <t>float|null</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>equity_snapshot</t>
+          <t>subscription_flow</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>snapshot_type</t>
+          <t>payment_method</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>str</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>equity_snapshot</t>
+          <t>subscription_flow</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>total_shares</t>
+          <t>subscription_ratio</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>float|null</t>
+          <t>str|null</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -2214,20 +2794,24 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>equity_snapshot</t>
+          <t>subscription_flow</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>total_capital</t>
+          <t>evidence_text</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>float|null</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>str(min=20)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2237,7 +2821,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>shareholder_name</t>
+          <t>source_page</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2259,15 +2843,19 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>shares_held</t>
+          <t>snapshot_date</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>float|null</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>str(YYYY-MM-DD)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2277,15 +2865,19 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>capital_contribution</t>
+          <t>snapshot_type</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>float|null</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2295,12 +2887,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>shareholding_ratio</t>
+          <t>total_shares</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>str|null</t>
+          <t>float|null</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -2313,433 +2905,269 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
+          <t>total_capital</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>float|null</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>equity_snapshot</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>shareholder_name</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>equity_snapshot</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>shares_held</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>float|null</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>equity_snapshot</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>capital_contribution</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>float|null</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>equity_snapshot</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>shareholding_ratio</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>str|null</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>equity_snapshot</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>snapshot_order</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>int|null</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>equity_snapshot</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>shareholder_type_detail</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>equity_snapshot</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>is_original_founder</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>yes/no/unknown</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>equity_snapshot</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
           <t>evidence_text</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>str(min=20)</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>Cross-Check 结果（相邻时点股本追踪 + 认缴存量对应）</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
         <is>
           <t>公司</t>
         </is>
       </c>
-      <c r="B24" s="1" t="inlineStr">
+      <c r="B32" s="1" t="inlineStr">
         <is>
           <t>上一时点</t>
         </is>
       </c>
-      <c r="C24" s="1" t="inlineStr">
+      <c r="C32" s="1" t="inlineStr">
         <is>
           <t>当前时点</t>
         </is>
       </c>
-      <c r="D24" s="1" t="inlineStr">
+      <c r="D32" s="1" t="inlineStr">
         <is>
           <t>股东名称</t>
         </is>
       </c>
-      <c r="E24" s="1" t="inlineStr">
+      <c r="E32" s="1" t="inlineStr">
         <is>
           <t>上一时点持股数
 (万股)</t>
         </is>
       </c>
-      <c r="F24" s="1" t="inlineStr">
+      <c r="F32" s="1" t="inlineStr">
         <is>
           <t>上一时点出资额
 (万元注册资本)</t>
         </is>
       </c>
-      <c r="G24" s="1" t="inlineStr">
+      <c r="G32" s="1" t="inlineStr">
         <is>
           <t>本次认缴/变化
 (万股)</t>
         </is>
       </c>
-      <c r="H24" s="1" t="inlineStr">
+      <c r="H32" s="1" t="inlineStr">
         <is>
           <t>预期变更后
 持股数(万股)</t>
         </is>
       </c>
-      <c r="I24" s="1" t="inlineStr">
+      <c r="I32" s="1" t="inlineStr">
         <is>
           <t>PDF披露
 持股数(万股)</t>
         </is>
       </c>
-      <c r="J24" s="1" t="inlineStr">
+      <c r="J32" s="1" t="inlineStr">
         <is>
           <t>差额(万股)</t>
         </is>
       </c>
-      <c r="K24" s="1" t="inlineStr">
+      <c r="K32" s="1" t="inlineStr">
         <is>
           <t>状态</t>
         </is>
       </c>
-      <c r="L24" s="1" t="inlineStr">
+      <c r="L32" s="1" t="inlineStr">
         <is>
           <t>说明</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>001282_三联锻造</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2004-06-18</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>2014-05</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>孙国奉</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>175.0</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>001282_三联锻造</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2004-06-18</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>2014-05</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>孙国敏</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>162.5</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>001282_三联锻造</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2004-06-18</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>2014-05</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>张松满</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>162.5</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>301563_云汉芯城</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2008-05-07</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>2014-08</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>武汉力源信息技术股份有限公司</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>301563_云汉芯城</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2008-05-07</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>2014-08</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>东方富海（上海）创业投资企业（有限合伙）</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>301563_云汉芯城</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2008-05-07</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>2014-08</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>深圳市云汉电子有限公司</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>25.0</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>301563_云汉芯城</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2008-05-07</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>2014-08</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>刘云锋</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>25.0</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>301563_云汉芯城</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2008-05-07</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>2014-08</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>301563_云汉芯城</t>
+          <t>001282_三联锻造</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2014-08</t>
+          <t>2004-06-18</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2015-08</t>
+          <t>2014-05</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>孙国奉</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>175.0</t>
+        </is>
+      </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
@@ -2749,35 +3177,35 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
+      <c r="L33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>301563_云汉芯城</t>
+          <t>001282_三联锻造</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2014-08</t>
+          <t>2004-06-18</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2015-08</t>
+          <t>2014-05</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>镇江红土创业投资有限公司</t>
+          <t>张松满</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>162.5</t>
+        </is>
+      </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
@@ -2787,35 +3215,35 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
+      <c r="L34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>301563_云汉芯城</t>
+          <t>001282_三联锻造</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2014-08</t>
+          <t>2004-06-18</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2015-08</t>
+          <t>2014-05</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>昆山红土高新创业投资有限公司</t>
+          <t>孙国敏</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>162.5</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
@@ -2827,7 +3255,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2839,17 +3267,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
+          <t>2008-05-07</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
           <t>2014-08</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>2015-08</t>
-        </is>
-      </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>深圳市创新投资集团有限公司</t>
+          <t>东方富海（上海）创业投资企业（有限合伙）</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
@@ -2877,21 +3305,25 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
+          <t>2008-05-07</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
           <t>2014-08</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>2015-08</t>
-        </is>
-      </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>东方富海（上海）创业投资企业（有限合伙）</t>
+          <t>刘云锋</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
@@ -2915,21 +3347,25 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
+          <t>2008-05-07</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
           <t>2014-08</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>2015-08</t>
-        </is>
-      </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>丰利财富（北京）国际资本管理股份有限公司</t>
+          <t>深圳市云汉电子有限公司</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
@@ -2941,7 +3377,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2953,17 +3389,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
+          <t>2008-05-07</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
           <t>2014-08</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>2015-08</t>
-        </is>
-      </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
@@ -2979,7 +3415,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2991,17 +3427,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
+          <t>2008-05-07</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
           <t>2014-08</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>2015-08</t>
-        </is>
-      </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
+          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
@@ -3029,17 +3465,17 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
+          <t>2014-08</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
           <t>2015-08</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>2015-12-03</t>
-        </is>
-      </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>曾烨</t>
+          <t>东方富海（上海）创业投资企业（有限合伙）</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
@@ -3055,7 +3491,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3067,17 +3503,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
+          <t>2014-08</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
           <t>2015-08</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>2015-12-03</t>
-        </is>
-      </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>丰利财富（北京）国际资本管理股份有限公司</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
@@ -3105,17 +3541,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
+          <t>2014-08</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
           <t>2015-08</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>2015-12-03</t>
-        </is>
-      </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>镇江红土创业投资有限公司</t>
+          <t>深圳市创新投资集团有限公司</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
@@ -3131,7 +3567,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3143,17 +3579,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
+          <t>2014-08</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
           <t>2015-08</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>2015-12-03</t>
-        </is>
-      </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>昆山红土高新创业投资有限公司</t>
+          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
@@ -3169,7 +3605,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3181,25 +3617,21 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
+          <t>2014-08</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
           <t>2015-08</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>2015-12-03</t>
-        </is>
-      </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>丰利财富（北京）国际资本管理股份有限公司</t>
+          <t>昆山红土高新创业投资有限公司</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
@@ -3211,7 +3643,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3223,17 +3655,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
+          <t>2014-08</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
           <t>2015-08</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>2015-12-03</t>
-        </is>
-      </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>深圳市创新投资集团有限公司</t>
+          <t>镇江红土创业投资有限公司</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
@@ -3249,7 +3681,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3261,17 +3693,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
+          <t>2014-08</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
           <t>2015-08</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>2015-12-03</t>
-        </is>
-      </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>刘云锋</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
@@ -3287,7 +3719,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3299,17 +3731,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
+          <t>2014-08</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
           <t>2015-08</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>2015-12-03</t>
-        </is>
-      </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
+          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
@@ -3337,17 +3769,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
+          <t>2015-08</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
           <t>2015-12-03</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>2018-06-28</t>
-        </is>
-      </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>曾烨</t>
+          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
@@ -3375,17 +3807,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
+          <t>2015-08</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
           <t>2015-12-03</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>2018-06-28</t>
-        </is>
-      </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>刘云锋</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
@@ -3401,7 +3833,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3413,21 +3845,25 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
+          <t>2015-08</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
           <t>2015-12-03</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>2018-06-28</t>
-        </is>
-      </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>夏东</t>
+          <t>丰利财富（北京）国际资本管理股份有限公司</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
@@ -3439,7 +3875,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3451,17 +3887,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
+          <t>2015-08</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
           <t>2015-12-03</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>2018-06-28</t>
-        </is>
-      </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>刘云锋</t>
+          <t>昆山红土高新创业投资有限公司</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
@@ -3489,17 +3925,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
+          <t>2015-08</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
           <t>2015-12-03</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>2018-06-28</t>
-        </is>
-      </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
+          <t>曾烨</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
@@ -3527,17 +3963,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
+          <t>2015-08</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
           <t>2015-12-03</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>2018-06-28</t>
-        </is>
-      </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
+          <t>镇江红土创业投资有限公司</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
@@ -3553,7 +3989,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3565,17 +4001,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
+          <t>2015-08</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
           <t>2015-12-03</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>2018-06-28</t>
-        </is>
-      </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
@@ -3603,17 +4039,17 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
+          <t>2015-08</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
           <t>2015-12-03</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>2018-06-28</t>
-        </is>
-      </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>CASREV FUND</t>
+          <t>深圳市创新投资集团有限公司</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
@@ -3629,7 +4065,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3651,7 +4087,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>珠海拓域投资合伙企业（有限合伙）</t>
+          <t>刘云锋</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
@@ -3667,7 +4103,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3679,25 +4115,21 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
+          <t>2015-12-03</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
           <t>2018-06-28</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>2020-05-28</t>
-        </is>
-      </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
+          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>7412.0</t>
-        </is>
-      </c>
+      <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
@@ -3709,7 +4141,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3721,25 +4153,21 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
+          <t>2015-12-03</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
           <t>2018-06-28</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>2020-05-28</t>
-        </is>
-      </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>珠海拓域投资合伙企业（有限合伙）</t>
+          <t>曾烨</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
@@ -3763,25 +4191,21 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
+          <t>2015-12-03</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
           <t>2018-06-28</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>2020-05-28</t>
-        </is>
-      </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
+          <t>夏东</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>1584.0</t>
-        </is>
-      </c>
+      <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
@@ -3793,7 +4217,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3805,17 +4229,17 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
+          <t>2015-12-03</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
           <t>2018-06-28</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>2020-05-28</t>
-        </is>
-      </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>火炬电子科技股份有限公司</t>
+          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
@@ -3843,25 +4267,21 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
+          <t>2015-12-03</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
           <t>2018-06-28</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>2020-05-28</t>
-        </is>
-      </c>
       <c r="D62" t="inlineStr">
         <is>
           <t>CASREV FUND</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
+      <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
@@ -3873,7 +4293,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3885,25 +4305,21 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
+          <t>2015-12-03</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
           <t>2018-06-28</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>2020-05-28</t>
-        </is>
-      </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>夏东</t>
+          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>204.0</t>
-        </is>
-      </c>
+      <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
@@ -3915,7 +4331,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3927,25 +4343,21 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
+          <t>2015-12-03</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
           <t>2018-06-28</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>2020-05-28</t>
-        </is>
-      </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
+          <t>珠海拓域投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>3000.0</t>
-        </is>
-      </c>
+      <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
@@ -3957,7 +4369,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3969,17 +4381,17 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2020-05-28</t>
+          <t>2015-12-03</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2020-09-23</t>
+          <t>2018-06-28</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>中小企业发展基金（深圳有限合伙）</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
@@ -3995,7 +4407,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4007,25 +4419,21 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
+          <t>2018-06-28</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
           <t>2020-05-28</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>2020-09-23</t>
-        </is>
-      </c>
       <c r="D66" t="inlineStr">
         <is>
           <t>火炬电子科技股份有限公司</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>5000.0</t>
-        </is>
-      </c>
+      <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
@@ -4037,7 +4445,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4049,21 +4457,25 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
+          <t>2018-06-28</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
           <t>2020-05-28</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>2020-09-23</t>
-        </is>
-      </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>厦门西堤股权投资合伙企业（有限合伙）</t>
+          <t>CASREV FUND</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr"/>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
@@ -4075,33 +4487,37 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>301581_黄山谷捷</t>
+          <t>301563_云汉芯城</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2012-06-12</t>
+          <t>2018-06-28</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2021-04-07</t>
+          <t>2020-05-28</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr"/>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>3000.0</t>
+        </is>
+      </c>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr"/>
@@ -4113,33 +4529,37 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>301581_黄山谷捷</t>
+          <t>301563_云汉芯城</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2012-06-12</t>
+          <t>2018-06-28</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2021-04-07</t>
+          <t>2020-05-28</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr"/>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>7412.0</t>
+        </is>
+      </c>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr"/>
@@ -4151,33 +4571,37 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>301581_黄山谷捷</t>
+          <t>301563_云汉芯城</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2012-06-12</t>
+          <t>2018-06-28</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2021-04-07</t>
+          <t>2020-05-28</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>张俊武</t>
+          <t>珠海拓域投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr"/>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
@@ -4189,35 +4613,35 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>301581_黄山谷捷</t>
+          <t>301563_云汉芯城</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2012-06-12</t>
+          <t>2018-06-28</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2021-04-07</t>
+          <t>2020-05-28</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>昆山谷捷金属制品有限公司</t>
+          <t>夏东</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
-          <t>1000.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="G71" t="inlineStr"/>
@@ -4238,26 +4662,30 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>301581_黄山谷捷</t>
+          <t>301563_云汉芯城</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2021-04-07</t>
+          <t>2018-06-28</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2021-04-13</t>
+          <t>2020-05-28</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>张俊武</t>
+          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr"/>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>1584.0</t>
+        </is>
+      </c>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr"/>
@@ -4267,31 +4695,39 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr"/>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>301581_黄山谷捷</t>
+          <t>301563_云汉芯城</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2021-04-07</t>
+          <t>2020-05-28</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2021-04-13</t>
+          <t>2020-09-23</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>火炬电子科技股份有限公司</t>
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr"/>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>5000.0</t>
+        </is>
+      </c>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr"/>
@@ -4301,27 +4737,31 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr"/>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>301581_黄山谷捷</t>
+          <t>301563_云汉芯城</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2021-04-07</t>
+          <t>2020-05-28</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2021-04-13</t>
+          <t>2020-09-23</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>厦门西堤股权投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
@@ -4335,27 +4775,31 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr"/>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>301581_黄山谷捷</t>
+          <t>301563_云汉芯城</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2021-04-13</t>
+          <t>2020-05-28</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2021-11-11</t>
+          <t>2020-09-23</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>张俊武</t>
+          <t>中小企业发展基金（深圳有限合伙）</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
@@ -4371,7 +4815,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4383,12 +4827,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2021-04-13</t>
+          <t>2012-06-12</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2021-11-11</t>
+          <t>2021-04-07</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -4409,7 +4853,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4421,17 +4865,17 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2021-04-13</t>
+          <t>2012-06-12</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2021-11-11</t>
+          <t>2021-04-07</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
+          <t>张俊武</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
@@ -4459,17 +4903,17 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2021-04-13</t>
+          <t>2012-06-12</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2021-11-11</t>
+          <t>2021-04-07</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>上海广弘实业有限公司</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
@@ -4497,21 +4941,25 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2021-04-13</t>
+          <t>2012-06-12</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2021-11-11</t>
+          <t>2021-04-07</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>昆山谷捷金属制品有限公司</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr"/>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr"/>
@@ -4535,25 +4983,21 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2021-11-11</t>
+          <t>2021-04-07</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2022-05-26</t>
+          <t>2021-04-13</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>1153.0</t>
-        </is>
-      </c>
+      <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr"/>
@@ -4563,11 +5007,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L80" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
+      <c r="L80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -4577,25 +5017,21 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2021-11-11</t>
+          <t>2021-04-07</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2022-05-26</t>
+          <t>2021-04-13</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>上海广弘实业有限公司</t>
+          <t>张俊武</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>10377.0</t>
-        </is>
-      </c>
+      <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr"/>
@@ -4605,11 +5041,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L81" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
+      <c r="L81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -4619,17 +5051,17 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2021-11-11</t>
+          <t>2021-04-07</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2022-05-26</t>
+          <t>2021-04-13</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>黄山佳捷股权管理中心（有限合伙）</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
@@ -4643,11 +5075,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
+      <c r="L82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -4657,17 +5085,17 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2022-05-26</t>
+          <t>2021-04-13</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2022-09-13</t>
+          <t>2021-11-11</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
@@ -4683,7 +5111,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4695,12 +5123,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2022-05-26</t>
+          <t>2021-04-13</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2022-09-13</t>
+          <t>2021-11-11</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -4721,7 +5149,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4733,12 +5161,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2022-05-26</t>
+          <t>2021-04-13</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2022-09-13</t>
+          <t>2021-11-11</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4771,12 +5199,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2022-05-26</t>
+          <t>2021-04-13</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2022-09-13</t>
+          <t>2021-11-11</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -4809,25 +5237,21 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2022-05-26</t>
+          <t>2021-04-13</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2022-09-13</t>
+          <t>2021-11-11</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>黄山佳捷股权管理中心（有限合伙）</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E87" t="inlineStr"/>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2124.81</t>
-        </is>
-      </c>
+      <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr"/>
@@ -4837,7 +5261,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L87" t="inlineStr"/>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -4847,21 +5275,25 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
+          <t>2021-11-11</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
           <t>2022-05-26</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>2022-09-13</t>
-        </is>
-      </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr"/>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>1153.0</t>
+        </is>
+      </c>
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr"/>
@@ -4873,49 +5305,37 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr"/>
+          <t>301581_黄山谷捷</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2021-11-11</t>
+        </is>
+      </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2022-05-26</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+          <t>黄山佳捷股权管理中心（有限合伙）</t>
         </is>
       </c>
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr"/>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>840.0</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>6999.972</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>7000.0</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>-0.028</t>
-        </is>
-      </c>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4923,49 +5343,41 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>price×shares vs amount diff=0.0%</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr"/>
+          <t>301581_黄山谷捷</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2021-11-11</t>
+        </is>
+      </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2022-05-26</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
+          <t>上海广弘实业有限公司</t>
         </is>
       </c>
       <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr"/>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>2999.988</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>3000.0</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>-0.012</t>
-        </is>
-      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>10377.0</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4973,49 +5385,37 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>price×shares vs amount diff=0.0%</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr"/>
+          <t>301581_黄山谷捷</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2022-05-26</t>
+        </is>
+      </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2022-09-13</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>上海骁墨信息技术服务中心(有限合伙)</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr"/>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>1499.994</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>1500.0</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>-0.006</t>
-        </is>
-      </c>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5023,49 +5423,37 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>price×shares vs amount diff=0.0%</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr"/>
+          <t>301581_黄山谷捷</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2022-05-26</t>
+        </is>
+      </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2022-09-13</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>深圳市杉晖创业投资合伙企业(有限合伙)</t>
+          <t>张俊武</t>
         </is>
       </c>
       <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr"/>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>297.3333</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>10000.0027</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>10000.0</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>0.0027</t>
-        </is>
-      </c>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5073,49 +5461,37 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>price×shares vs amount diff=0.0%</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr"/>
+          <t>301581_黄山谷捷</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2022-05-26</t>
+        </is>
+      </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2022-09-13</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>上海联炻企业管理中心(有限合伙)</t>
+          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
         </is>
       </c>
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr"/>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>297.3333</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>10000.0027</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>10000.0</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>0.0027</t>
-        </is>
-      </c>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5123,99 +5499,75 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>price×shares vs amount diff=0.0%</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr"/>
+          <t>301581_黄山谷捷</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2022-05-26</t>
+        </is>
+      </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2022-09-13</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>安吉璞颉企业管理合伙企业(有限合伙)</t>
+          <t>黄山佳捷股权管理中心（有限合伙）</t>
         </is>
       </c>
       <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr"/>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>148.6667</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>5000.0031</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>5000.0</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>0.0031</t>
-        </is>
-      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2124.81</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="L94" t="inlineStr">
-        <is>
-          <t>price×shares vs amount diff=0.0%</t>
-        </is>
-      </c>
+      <c r="L94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr"/>
+          <t>301581_黄山谷捷</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2022-05-26</t>
+        </is>
+      </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2022-09-13</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>江西赣江新区财投晨源股权投资中心(有限合伙)</t>
+          <t>上海广弘实业有限公司</t>
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr"/>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>89.2</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>3000.0012</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>3000.0</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>0.0012</t>
-        </is>
-      </c>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5223,49 +5575,37 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>price×shares vs amount diff=0.0%</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr"/>
+          <t>301581_黄山谷捷</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2022-05-26</t>
+        </is>
+      </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2022-09-13</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>深圳市达晨创程私募股权投资基金企业(有限合伙)</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr"/>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>86.5984</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>2912.5034</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>2912.5</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>0.0034</t>
-        </is>
-      </c>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5273,7 +5613,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>price×shares vs amount diff=0.0%</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5286,34 +5626,34 @@
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>上海杉创智至创业投资合伙企业(有限合伙)</t>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr">
         <is>
-          <t>59.4667</t>
+          <t>840.0</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2000.0019</t>
+          <t>6999.972</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>2000.0</t>
+          <t>7000.0</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>0.0019</t>
+          <t>-0.028</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -5336,34 +5676,34 @@
       <c r="B98" t="inlineStr"/>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>杭州达晨创程股权投资基金合伙企业(有限合伙)</t>
+          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr">
         <is>
-          <t>51.959</t>
+          <t>360.0</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>1747.5007</t>
+          <t>2999.988</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>1747.5</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>0.0007</t>
+          <t>-0.012</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -5386,34 +5726,34 @@
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙)</t>
+          <t>上海骁墨信息技术服务中心(有限合伙)</t>
         </is>
       </c>
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>999.9993</t>
+          <t>1499.994</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>1000.0</t>
+          <t>1500.0</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>-0.0007</t>
+          <t>-0.006</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -5441,29 +5781,29 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>深圳市达晨财智创业投资管理有限公司</t>
+          <t>深圳市杉晖创业投资合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>999.9993</t>
+          <t>10000.0027</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>1000.0</t>
+          <t>10000.0</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>-0.0007</t>
+          <t>0.0027</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -5491,29 +5831,29 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>深圳市财智创赢私募股权投资企业(有限合伙)</t>
+          <t>上海联炻企业管理中心(有限合伙)</t>
         </is>
       </c>
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
         <is>
-          <t>10.1093</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>339.999</t>
+          <t>10000.0027</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>340.0</t>
+          <t>10000.0</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>-0.001</t>
+          <t>0.0027</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -5533,35 +5873,39 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>1992-12-04</t>
-        </is>
-      </c>
+      <c r="B102" t="inlineStr"/>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
+          <t>安吉璞颉企业管理合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr">
         <is>
-          <t>1020.0</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr"/>
+          <t>148.6667</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>5000.0031</t>
+        </is>
+      </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>1020.0</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr"/>
+          <t>5000.0</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>0.0031</t>
+        </is>
+      </c>
       <c r="K102" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5569,7 +5913,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
@@ -5579,35 +5923,39 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>1992-12-04</t>
-        </is>
-      </c>
+      <c r="B103" t="inlineStr"/>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
+          <t>江西赣江新区财投晨源股权投资中心(有限合伙)</t>
         </is>
       </c>
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
         <is>
-          <t>1800.0</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr"/>
+          <t>89.2</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>3000.0012</t>
+        </is>
+      </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>1800.0</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr"/>
+          <t>3000.0</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>0.0012</t>
+        </is>
+      </c>
       <c r="K103" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5615,7 +5963,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
@@ -5625,27 +5973,39 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>1992-12-04</t>
-        </is>
-      </c>
+      <c r="B104" t="inlineStr"/>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>友升太平洋(美国)投资有限公司</t>
+          <t>深圳市达晨创程私募股权投资基金企业(有限合伙)</t>
         </is>
       </c>
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr"/>
-      <c r="G104" t="inlineStr"/>
-      <c r="H104" t="inlineStr"/>
-      <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>86.5984</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>2912.5034</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>2912.5</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>0.0034</t>
+        </is>
+      </c>
       <c r="K104" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5653,7 +6013,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
@@ -5663,35 +6023,39 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>1992-12-04</t>
-        </is>
-      </c>
+      <c r="B105" t="inlineStr"/>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>上海泽升贸易有限公司</t>
+          <t>上海杉创智至创业投资合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr">
         <is>
-          <t>8976.0</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr"/>
+          <t>59.4667</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>2000.0019</t>
+        </is>
+      </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>8976.0</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr"/>
+          <t>2000.0</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>0.0019</t>
+        </is>
+      </c>
       <c r="K105" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5699,7 +6063,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
@@ -5709,27 +6073,39 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>1992-12-04</t>
-        </is>
-      </c>
+      <c r="B106" t="inlineStr"/>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>上海市青浦县徐泾乡工业公司</t>
+          <t>杭州达晨创程股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr"/>
-      <c r="G106" t="inlineStr"/>
-      <c r="H106" t="inlineStr"/>
-      <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>51.959</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>1747.5007</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>1747.5</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>0.0007</t>
+        </is>
+      </c>
       <c r="K106" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5737,7 +6113,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
@@ -5747,35 +6123,39 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>1992-12-04</t>
-        </is>
-      </c>
+      <c r="B107" t="inlineStr"/>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>罗世兵</t>
+          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr">
         <is>
-          <t>204.0</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr"/>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>999.9993</t>
+        </is>
+      </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>204.0</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr"/>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>-0.0007</t>
+        </is>
+      </c>
       <c r="K107" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5783,7 +6163,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
@@ -5793,39 +6173,39 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>2020-09-09</t>
-        </is>
-      </c>
+      <c r="B108" t="inlineStr"/>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>1020.0</t>
-        </is>
-      </c>
+          <t>深圳市达晨财智创业投资管理有限公司</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
         <is>
-          <t>1020.0</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2040.0</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
+          <t>999.9993</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>-0.0007</t>
+        </is>
+      </c>
       <c r="K108" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5833,7 +6213,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
@@ -5843,39 +6223,39 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>2020-09-09</t>
-        </is>
-      </c>
+      <c r="B109" t="inlineStr"/>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
+          <t>深圳市财智创赢私募股权投资企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>10.1093</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>3600.0</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
+          <t>339.999</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>340.0</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>-0.001</t>
+        </is>
+      </c>
       <c r="K109" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5883,7 +6263,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
@@ -5895,30 +6275,30 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
+          <t>1992-12-04</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
           <t>2020-09-09</t>
         </is>
       </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>2020-09-27</t>
-        </is>
-      </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+          <t>上海泽升贸易有限公司</t>
         </is>
       </c>
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr">
         <is>
-          <t>840.0</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="H110" t="inlineStr"/>
       <c r="I110" t="inlineStr">
         <is>
-          <t>840.0</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="J110" t="inlineStr"/>
@@ -5941,36 +6321,32 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
+          <t>1992-12-04</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
           <t>2020-09-09</t>
         </is>
       </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>2020-09-27</t>
-        </is>
-      </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>上海泽升贸易有限公司</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>8976.0</t>
-        </is>
-      </c>
+          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
         <is>
-          <t>8976.0</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>17952.0</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr"/>
+          <t>1800.0</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr">
         <is>
@@ -5979,7 +6355,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5991,32 +6367,24 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
+          <t>1992-12-04</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
           <t>2020-09-09</t>
         </is>
       </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>2020-09-27</t>
-        </is>
-      </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>上海骁墨信息技术服务中心(有限合伙)</t>
+          <t>上海市青浦县徐泾乡工业公司</t>
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr"/>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
+      <c r="G112" t="inlineStr"/>
       <c r="H112" t="inlineStr"/>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
+      <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr">
         <is>
@@ -6025,7 +6393,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -6037,36 +6405,32 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
+          <t>1992-12-04</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
           <t>2020-09-09</t>
         </is>
       </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>2020-09-27</t>
-        </is>
-      </c>
       <c r="D113" t="inlineStr">
         <is>
           <t>罗世兵</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>204.0</t>
-        </is>
-      </c>
+      <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
           <t>204.0</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>408.0</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr"/>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>204.0</t>
+        </is>
+      </c>
       <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr">
         <is>
@@ -6075,7 +6439,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6087,32 +6451,24 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
+          <t>1992-12-04</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
           <t>2020-09-09</t>
         </is>
       </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>2020-09-27</t>
-        </is>
-      </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
+          <t>友升太平洋(美国)投资有限公司</t>
         </is>
       </c>
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr"/>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
+      <c r="G114" t="inlineStr"/>
       <c r="H114" t="inlineStr"/>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
+      <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr">
         <is>
@@ -6121,7 +6477,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -6133,40 +6489,32 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>1992-12-04</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>840.0</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>7000.0</t>
-        </is>
-      </c>
+          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr"/>
+      <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr">
         <is>
-          <t>840.0</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>1680.0</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr"/>
+          <t>1020.0</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>1020.0</t>
+        </is>
+      </c>
       <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr">
         <is>
@@ -6175,7 +6523,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6187,32 +6535,36 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
+          <t>2020-09-09</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
           <t>2020-09-27</t>
         </is>
       </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>2022-12-19</t>
-        </is>
-      </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>江西赣江新区财投晨源股权投资中心(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr"/>
+          <t>上海泽升贸易有限公司</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>8976.0</t>
+        </is>
+      </c>
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
         <is>
-          <t>89.2</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr"/>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>89.2</t>
-        </is>
-      </c>
+          <t>8976.0</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>17952.0</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr">
         <is>
@@ -6221,7 +6573,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -6233,30 +6585,30 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
+          <t>2020-09-09</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
           <t>2020-09-27</t>
         </is>
       </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>2022-12-19</t>
-        </is>
-      </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>杭州达晨创程股权投资基金合伙企业(有限合伙)</t>
+          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr">
         <is>
-          <t>51.959</t>
+          <t>360.0</t>
         </is>
       </c>
       <c r="H117" t="inlineStr"/>
       <c r="I117" t="inlineStr">
         <is>
-          <t>51.959</t>
+          <t>360.0</t>
         </is>
       </c>
       <c r="J117" t="inlineStr"/>
@@ -6279,32 +6631,36 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
+          <t>2020-09-09</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
           <t>2020-09-27</t>
         </is>
       </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>2022-12-19</t>
-        </is>
-      </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>上海联炻企业管理中心(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr"/>
+          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr">
         <is>
-          <t>297.3333</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr"/>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>297.3333</t>
-        </is>
-      </c>
+          <t>1800.0</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>3600.0</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr">
         <is>
@@ -6313,7 +6669,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -6325,40 +6681,32 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
+          <t>2020-09-09</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
           <t>2020-09-27</t>
         </is>
       </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>2022-12-19</t>
-        </is>
-      </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>3000.0</t>
-        </is>
-      </c>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr"/>
+      <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr">
         <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>720.0</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr"/>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr">
         <is>
@@ -6367,7 +6715,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6379,32 +6727,36 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
+          <t>2020-09-09</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
           <t>2020-09-27</t>
         </is>
       </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>2022-12-19</t>
-        </is>
-      </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>深圳市达晨财智创业投资管理有限公司</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr"/>
+          <t>罗世兵</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>204.0</t>
+        </is>
+      </c>
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr">
         <is>
-          <t>29.7333</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr"/>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>29.7333</t>
-        </is>
-      </c>
+          <t>204.0</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>408.0</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr">
         <is>
@@ -6413,7 +6765,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -6425,30 +6777,30 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
+          <t>2020-09-09</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
           <t>2020-09-27</t>
         </is>
       </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>2022-12-19</t>
-        </is>
-      </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙)</t>
+          <t>上海骁墨信息技术服务中心(有限合伙)</t>
         </is>
       </c>
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="H121" t="inlineStr"/>
       <c r="I121" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="J121" t="inlineStr"/>
@@ -6471,37 +6823,33 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
+          <t>2020-09-09</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
           <t>2020-09-27</t>
         </is>
       </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>2022-12-19</t>
-        </is>
-      </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>上海骁墨信息技术服务中心(有限合伙)</t>
+          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>1500.0</t>
-        </is>
-      </c>
+          <t>1020.0</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr"/>
       <c r="G122" t="inlineStr">
         <is>
-          <t>180.0</t>
+          <t>1020.0</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>360.0</t>
+          <t>2040.0</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -6535,20 +6883,20 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>深圳市杉晖创业投资合伙企业(有限合伙)</t>
+          <t>江西赣江新区财投晨源股权投资中心(有限合伙)</t>
         </is>
       </c>
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="J123" t="inlineStr"/>
@@ -6581,20 +6929,20 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>深圳市达晨创程私募股权投资基金企业(有限合伙)</t>
+          <t>上海联炻企业管理中心(有限合伙)</t>
         </is>
       </c>
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr">
         <is>
-          <t>86.5984</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr">
         <is>
-          <t>86.5984</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="J124" t="inlineStr"/>
@@ -6627,20 +6975,20 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>上海杉创智至创业投资合伙企业(有限合伙)</t>
+          <t>深圳市达晨创程私募股权投资基金企业(有限合伙)</t>
         </is>
       </c>
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr"/>
       <c r="G125" t="inlineStr">
         <is>
-          <t>59.4667</t>
+          <t>86.5984</t>
         </is>
       </c>
       <c r="H125" t="inlineStr"/>
       <c r="I125" t="inlineStr">
         <is>
-          <t>59.4667</t>
+          <t>86.5984</t>
         </is>
       </c>
       <c r="J125" t="inlineStr"/>
@@ -6673,20 +7021,20 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>深圳市财智创赢私募股权投资企业(有限合伙)</t>
+          <t>深圳市达晨财智创业投资管理有限公司</t>
         </is>
       </c>
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr">
         <is>
-          <t>10.1093</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="H126" t="inlineStr"/>
       <c r="I126" t="inlineStr">
         <is>
-          <t>10.1093</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="J126" t="inlineStr"/>
@@ -6719,20 +7067,20 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>安吉璞颉企业管理合伙企业(有限合伙)</t>
+          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr"/>
       <c r="G127" t="inlineStr">
         <is>
-          <t>148.6667</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="H127" t="inlineStr"/>
       <c r="I127" t="inlineStr">
         <is>
-          <t>148.6667</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="J127" t="inlineStr"/>
@@ -6753,39 +7101,43 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B128" t="inlineStr"/>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>上海泽升贸易有限公司 (认缴→存量)</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr"/>
-      <c r="F128" t="inlineStr"/>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>7000.0</t>
+        </is>
+      </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>8976.0</t>
+          <t>840.0</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>8976.0</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>8976.0</t>
-        </is>
-      </c>
-      <c r="J128" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>1680.0</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -6793,7 +7145,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -6803,39 +7155,35 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B129" t="inlineStr"/>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
+          <t>杭州达晨创程股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr">
         <is>
-          <t>1800.0</t>
-        </is>
-      </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
+          <t>51.959</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr"/>
       <c r="I129" t="inlineStr">
         <is>
-          <t>1800.0</t>
-        </is>
-      </c>
-      <c r="J129" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>51.959</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr"/>
       <c r="K129" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -6843,7 +7191,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6853,39 +7201,35 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B130" t="inlineStr"/>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>共青城泽升投资管理合伙企业(有限合伙) (认缴→存量)</t>
+          <t>上海杉创智至创业投资合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr"/>
       <c r="G130" t="inlineStr">
         <is>
-          <t>1020.0</t>
-        </is>
-      </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>1020.0</t>
-        </is>
-      </c>
+          <t>59.4667</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr"/>
       <c r="I130" t="inlineStr">
         <is>
-          <t>1020.0</t>
-        </is>
-      </c>
-      <c r="J130" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>59.4667</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -6893,7 +7237,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6903,39 +7247,35 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B131" t="inlineStr"/>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>罗世兵 (认缴→存量)</t>
+          <t>深圳市财智创赢私募股权投资企业(有限合伙)</t>
         </is>
       </c>
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr"/>
       <c r="G131" t="inlineStr">
         <is>
-          <t>204.0</t>
-        </is>
-      </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>204.0</t>
-        </is>
-      </c>
+          <t>10.1093</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr"/>
       <c r="I131" t="inlineStr">
         <is>
-          <t>204.0</t>
-        </is>
-      </c>
-      <c r="J131" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>10.1093</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr"/>
       <c r="K131" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -6943,7 +7283,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6953,39 +7293,43 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B132" t="inlineStr"/>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr"/>
-      <c r="F132" t="inlineStr"/>
+          <t>上海骁墨信息技术服务中心(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>1500.0</t>
+        </is>
+      </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>840.0</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>840.0</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>840.0</t>
-        </is>
-      </c>
-      <c r="J132" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -6993,7 +7337,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -7003,39 +7347,35 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B133" t="inlineStr"/>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
+          <t>深圳市杉晖创业投资合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr"/>
       <c r="G133" t="inlineStr">
         <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
+          <t>297.3333</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr"/>
       <c r="I133" t="inlineStr">
         <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="J133" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>297.3333</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -7043,7 +7383,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -7053,39 +7393,35 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B134" t="inlineStr"/>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>上海骁墨信息技术服务中心(有限合伙) (认缴→存量)</t>
+          <t>安吉璞颉企业管理合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr">
         <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
+          <t>148.6667</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr"/>
       <c r="I134" t="inlineStr">
         <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="J134" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>148.6667</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr"/>
       <c r="K134" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -7093,7 +7429,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -7103,7 +7439,11 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B135" t="inlineStr"/>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
       <c r="C135" t="inlineStr">
         <is>
           <t>2022-12-19</t>
@@ -7111,31 +7451,31 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>深圳市杉晖创业投资合伙企业(有限合伙) (认缴→存量)</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr"/>
-      <c r="F135" t="inlineStr"/>
+          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>3000.0</t>
+        </is>
+      </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>360.0</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>297.3333</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>297.3333</t>
-        </is>
-      </c>
-      <c r="J135" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>720.0</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
+      <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -7143,7 +7483,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -7156,29 +7496,29 @@
       <c r="B136" t="inlineStr"/>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>上海联炻企业管理中心(有限合伙) (认缴→存量)</t>
+          <t>上海泽升贸易有限公司 (认缴→存量)</t>
         </is>
       </c>
       <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr"/>
       <c r="G136" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -7206,29 +7546,29 @@
       <c r="B137" t="inlineStr"/>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>安吉璞颉企业管理合伙企业(有限合伙) (认缴→存量)</t>
+          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr"/>
       <c r="G137" t="inlineStr">
         <is>
-          <t>148.6667</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>148.6667</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>148.6667</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -7256,29 +7596,29 @@
       <c r="B138" t="inlineStr"/>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>江西赣江新区财投晨源股权投资中心(有限合伙) (认缴→存量)</t>
+          <t>共青城泽升投资管理合伙企业(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr"/>
       <c r="G138" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>1020.0</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>1020.0</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>1020.0</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -7306,29 +7646,29 @@
       <c r="B139" t="inlineStr"/>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>深圳市达晨创程私募股权投资基金企业(有限合伙) (认缴→存量)</t>
+          <t>罗世兵 (认缴→存量)</t>
         </is>
       </c>
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr"/>
       <c r="G139" t="inlineStr">
         <is>
-          <t>86.5984</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>86.5984</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>86.5984</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -7356,29 +7696,29 @@
       <c r="B140" t="inlineStr"/>
       <c r="C140" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>上海杉创智至创业投资合伙企业(有限合伙) (认缴→存量)</t>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr"/>
       <c r="G140" t="inlineStr">
         <is>
-          <t>59.4667</t>
+          <t>840.0</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>59.4667</t>
+          <t>840.0</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>59.4667</t>
+          <t>840.0</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -7406,29 +7746,29 @@
       <c r="B141" t="inlineStr"/>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>杭州达晨创程股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
+          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr"/>
       <c r="G141" t="inlineStr">
         <is>
-          <t>51.959</t>
+          <t>360.0</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>51.959</t>
+          <t>360.0</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>51.959</t>
+          <t>360.0</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -7456,29 +7796,29 @@
       <c r="B142" t="inlineStr"/>
       <c r="C142" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
+          <t>上海骁墨信息技术服务中心(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr"/>
       <c r="G142" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -7511,24 +7851,24 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>深圳市达晨财智创业投资管理有限公司 (认缴→存量)</t>
+          <t>深圳市杉晖创业投资合伙企业(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr"/>
       <c r="G143" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -7561,24 +7901,24 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>深圳市财智创赢私募股权投资企业(有限合伙) (认缴→存量)</t>
+          <t>上海联炻企业管理中心(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr"/>
       <c r="G144" t="inlineStr">
         <is>
-          <t>10.1093</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>10.1093</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>10.1093</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -7600,30 +7940,42 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>688758_赛分科技</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>2011-10</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr"/>
       <c r="C145" t="inlineStr">
         <is>
-          <t>2021-09-16</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>高新同华</t>
+          <t>安吉璞颉企业管理合伙企业(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr"/>
-      <c r="G145" t="inlineStr"/>
-      <c r="H145" t="inlineStr"/>
-      <c r="I145" t="inlineStr"/>
-      <c r="J145" t="inlineStr"/>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>148.6667</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>148.6667</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>148.6667</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K145" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -7631,37 +7983,49 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>认购数 vs 存量持股数</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>688758_赛分科技</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>2011-10</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr"/>
       <c r="C146" t="inlineStr">
         <is>
-          <t>2021-09-16</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>黄学英</t>
+          <t>江西赣江新区财投晨源股权投资中心(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr"/>
-      <c r="G146" t="inlineStr"/>
-      <c r="H146" t="inlineStr"/>
-      <c r="I146" t="inlineStr"/>
-      <c r="J146" t="inlineStr"/>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>89.2</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>89.2</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>89.2</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K146" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -7669,37 +8033,49 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>认购数 vs 存量持股数</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>688758_赛分科技</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>2011-10</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr"/>
       <c r="C147" t="inlineStr">
         <is>
-          <t>2021-09-16</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>周乃鼎</t>
+          <t>深圳市达晨创程私募股权投资基金企业(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr"/>
-      <c r="G147" t="inlineStr"/>
-      <c r="H147" t="inlineStr"/>
-      <c r="I147" t="inlineStr"/>
-      <c r="J147" t="inlineStr"/>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>86.5984</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>86.5984</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>86.5984</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K147" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -7707,71 +8083,99 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>认购数 vs 存量持股数</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>688758_赛分科技</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>2011-10</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr"/>
       <c r="C148" t="inlineStr">
         <is>
-          <t>2021-09-16</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>陆民</t>
+          <t>上海杉创智至创业投资合伙企业(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr"/>
-      <c r="G148" t="inlineStr"/>
-      <c r="H148" t="inlineStr"/>
-      <c r="I148" t="inlineStr"/>
-      <c r="J148" t="inlineStr"/>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>59.4667</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>59.4667</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>59.4667</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K148" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="L148" t="inlineStr"/>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>688758_赛分科技</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>2011-10</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr"/>
       <c r="C149" t="inlineStr">
         <is>
-          <t>2021-09-16</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>华泰大健康一号</t>
+          <t>杭州达晨创程股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr"/>
-      <c r="G149" t="inlineStr"/>
-      <c r="H149" t="inlineStr"/>
-      <c r="I149" t="inlineStr"/>
-      <c r="J149" t="inlineStr"/>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>51.959</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>51.959</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>51.959</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K149" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -7779,37 +8183,49 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>认购数 vs 存量持股数</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>688758_赛分科技</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>2011-10</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr"/>
       <c r="C150" t="inlineStr">
         <is>
-          <t>2021-09-16</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>复星惟盈</t>
+          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr"/>
-      <c r="G150" t="inlineStr"/>
-      <c r="H150" t="inlineStr"/>
-      <c r="I150" t="inlineStr"/>
-      <c r="J150" t="inlineStr"/>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K150" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -7817,37 +8233,49 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>认购数 vs 存量持股数</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>688758_赛分科技</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>2011-10</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr"/>
       <c r="C151" t="inlineStr">
         <is>
-          <t>2021-09-16</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>国寿疌泉</t>
+          <t>深圳市达晨财智创业投资管理有限公司 (认缴→存量)</t>
         </is>
       </c>
       <c r="E151" t="inlineStr"/>
       <c r="F151" t="inlineStr"/>
-      <c r="G151" t="inlineStr"/>
-      <c r="H151" t="inlineStr"/>
-      <c r="I151" t="inlineStr"/>
-      <c r="J151" t="inlineStr"/>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K151" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -7855,37 +8283,49 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>认购数 vs 存量持股数</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>688758_赛分科技</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>2011-10</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr"/>
       <c r="C152" t="inlineStr">
         <is>
-          <t>2021-09-16</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>史建伟</t>
+          <t>深圳市财智创赢私募股权投资企业(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr"/>
-      <c r="G152" t="inlineStr"/>
-      <c r="H152" t="inlineStr"/>
-      <c r="I152" t="inlineStr"/>
-      <c r="J152" t="inlineStr"/>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>10.1093</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>10.1093</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>10.1093</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K152" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -7893,7 +8333,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>认购数 vs 存量持股数</t>
         </is>
       </c>
     </row>
@@ -7915,7 +8355,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>黄学英/刘鸿雁</t>
+          <t>周乃鼎</t>
         </is>
       </c>
       <c r="E153" t="inlineStr"/>
@@ -7953,7 +8393,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>周金清</t>
+          <t>黄学英</t>
         </is>
       </c>
       <c r="E154" t="inlineStr"/>
@@ -7991,7 +8431,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Cheer Rise Consultants Limited</t>
+          <t>周金清</t>
         </is>
       </c>
       <c r="E155" t="inlineStr"/>
@@ -8007,7 +8447,7 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -8029,7 +8469,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>苏州贤达</t>
+          <t>国寿疌泉</t>
         </is>
       </c>
       <c r="E156" t="inlineStr"/>
@@ -8052,22 +8492,22 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
+          <t>688758_赛分科技</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2015-01</t>
+          <t>2011-10</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2021-09-16</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>陆民</t>
         </is>
       </c>
       <c r="E157" t="inlineStr"/>
@@ -8081,31 +8521,27 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L157" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
+      <c r="L157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
+          <t>688758_赛分科技</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2015-01</t>
+          <t>2011-10</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2021-09-16</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>Cheer Rise Consultants Limited</t>
         </is>
       </c>
       <c r="E158" t="inlineStr"/>
@@ -8128,22 +8564,22 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
+          <t>688758_赛分科技</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2015-01</t>
+          <t>2011-10</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2021-09-16</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>华金同达（深圳）投资合伙企业（有限合伙）</t>
+          <t>复星惟盈</t>
         </is>
       </c>
       <c r="E159" t="inlineStr"/>
@@ -8159,29 +8595,29 @@
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
+          <t>688758_赛分科技</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2015-01</t>
+          <t>2011-10</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2021-09-16</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>深圳市伊敦传媒投资基金合伙企业（有限合伙）</t>
+          <t>高新同华</t>
         </is>
       </c>
       <c r="E160" t="inlineStr"/>
@@ -8197,29 +8633,29 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
+          <t>688758_赛分科技</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2015-01</t>
+          <t>2011-10</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2021-09-16</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>苏州贤达</t>
         </is>
       </c>
       <c r="E161" t="inlineStr"/>
@@ -8235,29 +8671,29 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
+          <t>688758_赛分科技</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2015-01</t>
+          <t>2011-10</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2021-09-16</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>金石智娱股权投资（深圳）合伙企业（有限合伙）</t>
+          <t>黄学英/刘鸿雁</t>
         </is>
       </c>
       <c r="E162" t="inlineStr"/>
@@ -8280,22 +8716,22 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
+          <t>688758_赛分科技</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2015-01</t>
+          <t>2011-10</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2021-09-16</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>华泰大健康一号</t>
         </is>
       </c>
       <c r="E163" t="inlineStr"/>
@@ -8318,22 +8754,22 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
+          <t>688758_赛分科技</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2015-01</t>
+          <t>2011-10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2021-09-16</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>深圳中证投资有限责任公司</t>
+          <t>史建伟</t>
         </is>
       </c>
       <c r="E164" t="inlineStr"/>
@@ -8371,7 +8807,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>厦门富凯海创投资管理有限责任公司</t>
+          <t>深圳中证投资有限责任公司</t>
         </is>
       </c>
       <c r="E165" t="inlineStr"/>
@@ -8399,17 +8835,17 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
           <t>2015-07-09</t>
         </is>
       </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>2020-02-26</t>
-        </is>
-      </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>QM101 Limited</t>
         </is>
       </c>
       <c r="E166" t="inlineStr"/>
@@ -8425,7 +8861,7 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -8437,17 +8873,17 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
           <t>2015-07-09</t>
         </is>
       </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>2020-02-26</t>
-        </is>
-      </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>深圳市伊敦传媒投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E167" t="inlineStr"/>
@@ -8463,7 +8899,7 @@
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -8475,25 +8911,21 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
           <t>2015-07-09</t>
         </is>
       </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>2020-02-26</t>
-        </is>
-      </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>香港迅雷有限公司</t>
         </is>
       </c>
       <c r="E168" t="inlineStr"/>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F168" t="inlineStr"/>
       <c r="G168" t="inlineStr"/>
       <c r="H168" t="inlineStr"/>
       <c r="I168" t="inlineStr"/>
@@ -8503,7 +8935,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L168" t="inlineStr"/>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -8513,17 +8949,17 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
           <t>2015-07-09</t>
         </is>
       </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>2020-02-26</t>
-        </is>
-      </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>华金同达（深圳）投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E169" t="inlineStr"/>
@@ -8539,7 +8975,7 @@
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -8551,17 +8987,17 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>2015-01</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>2023-03-24</t>
+          <t>2015-07-09</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>厦门富凯海创投资管理有限责任公司</t>
         </is>
       </c>
       <c r="E170" t="inlineStr"/>
@@ -8589,17 +9025,17 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>2015-01</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>2023-03-24</t>
+          <t>2015-07-09</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>北京岚锋创视网络科技有限公司</t>
         </is>
       </c>
       <c r="E171" t="inlineStr"/>
@@ -8615,7 +9051,7 @@
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -8627,17 +9063,17 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>2015-01</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>2023-03-24</t>
+          <t>2015-07-09</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>汇智同裕（深圳）投资合伙企业（有限合伙）</t>
+          <t>金石智娱股权投资（深圳）合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E172" t="inlineStr"/>
@@ -8653,7 +9089,7 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -8665,17 +9101,17 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>2015-01</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>2023-03-24</t>
+          <t>2015-07-09</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>EARN ACE LIMITED</t>
         </is>
       </c>
       <c r="E173" t="inlineStr"/>
@@ -8703,21 +9139,25 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
           <t>2020-02-26</t>
         </is>
       </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>2023-03-24</t>
-        </is>
-      </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>北京岚锋创视网络科技有限公司</t>
         </is>
       </c>
       <c r="E174" t="inlineStr"/>
-      <c r="F174" t="inlineStr"/>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G174" t="inlineStr"/>
       <c r="H174" t="inlineStr"/>
       <c r="I174" t="inlineStr"/>
@@ -8727,51 +9167,35 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L174" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
+      <c r="L174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>920100_三协电机</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr"/>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>2023-09-06</t>
+          <t>2020-02-26</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>盛祎等15名自然人</t>
+          <t>QM101 Limited</t>
         </is>
       </c>
       <c r="E175" t="inlineStr"/>
       <c r="F175" t="inlineStr"/>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>321.5</t>
-        </is>
-      </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>1739.315</t>
-        </is>
-      </c>
-      <c r="I175" t="inlineStr">
-        <is>
-          <t>1723.09</t>
-        </is>
-      </c>
-      <c r="J175" t="inlineStr">
-        <is>
-          <t>16.225</t>
-        </is>
-      </c>
+      <c r="G175" t="inlineStr"/>
+      <c r="H175" t="inlineStr"/>
+      <c r="I175" t="inlineStr"/>
+      <c r="J175" t="inlineStr"/>
       <c r="K175" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -8779,29 +9203,29 @@
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>price×shares vs amount diff=0.9%</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>920100_三协电机</t>
+          <t>688775_影石创新</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2002-11-07</t>
+          <t>2015-07-09</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>2022-08-09</t>
+          <t>2020-02-26</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>深圳市稳正景明创业投资企业(有限合伙)</t>
+          <t>EARN ACE LIMITED</t>
         </is>
       </c>
       <c r="E176" t="inlineStr"/>
@@ -8824,22 +9248,22 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>920100_三协电机</t>
+          <t>688775_影石创新</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2002-11-07</t>
+          <t>2015-07-09</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>2022-08-09</t>
+          <t>2020-02-26</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>盛祎</t>
+          <t>香港迅雷有限公司</t>
         </is>
       </c>
       <c r="E177" t="inlineStr"/>
@@ -8855,29 +9279,29 @@
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>920100_三协电机</t>
+          <t>688775_影石创新</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2002-11-07</t>
+          <t>2020-02-26</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>2022-08-09</t>
+          <t>2023-03-24</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>朱绶青</t>
+          <t>汇智同裕（深圳）投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E178" t="inlineStr"/>
@@ -8893,29 +9317,29 @@
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>688775_影石创新</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2016-12-14</t>
+          <t>2020-02-26</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2023-03-24</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>牛威</t>
+          <t>北京岚锋创视网络科技有限公司</t>
         </is>
       </c>
       <c r="E179" t="inlineStr"/>
@@ -8931,29 +9355,29 @@
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>688775_影石创新</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2016-12-14</t>
+          <t>2020-02-26</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2023-03-24</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>吴功友</t>
+          <t>QM101 Limited</t>
         </is>
       </c>
       <c r="E180" t="inlineStr"/>
@@ -8969,37 +9393,33 @@
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>688775_影石创新</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2016-12-14</t>
+          <t>2020-02-26</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2023-03-24</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>吴功友(王金林代持)</t>
+          <t>EARN ACE LIMITED</t>
         </is>
       </c>
       <c r="E181" t="inlineStr"/>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>400.0</t>
-        </is>
-      </c>
+      <c r="F181" t="inlineStr"/>
       <c r="G181" t="inlineStr"/>
       <c r="H181" t="inlineStr"/>
       <c r="I181" t="inlineStr"/>
@@ -9018,30 +9438,26 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>688775_影石创新</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2016-12-14</t>
+          <t>2020-02-26</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2023-03-24</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>四方股份</t>
+          <t>香港迅雷有限公司</t>
         </is>
       </c>
       <c r="E182" t="inlineStr"/>
-      <c r="F182" t="inlineStr">
-        <is>
-          <t>1200.0</t>
-        </is>
-      </c>
+      <c r="F182" t="inlineStr"/>
       <c r="G182" t="inlineStr"/>
       <c r="H182" t="inlineStr"/>
       <c r="I182" t="inlineStr"/>
@@ -9060,34 +9476,42 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>2016-12-14</t>
-        </is>
-      </c>
+          <t>920100_三协电机</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr"/>
       <c r="C183" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2023-09-06</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>牛威(罗永红代持)</t>
+          <t>盛祎等15名自然人</t>
         </is>
       </c>
       <c r="E183" t="inlineStr"/>
-      <c r="F183" t="inlineStr">
-        <is>
-          <t>400.0</t>
-        </is>
-      </c>
-      <c r="G183" t="inlineStr"/>
-      <c r="H183" t="inlineStr"/>
-      <c r="I183" t="inlineStr"/>
-      <c r="J183" t="inlineStr"/>
+      <c r="F183" t="inlineStr"/>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>321.5</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>1739.315</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>1723.09</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>16.225</t>
+        </is>
+      </c>
       <c r="K183" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -9095,44 +9519,36 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>price×shares vs amount diff=0.9%</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>920100_三协电机</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2002-11-07</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-08-09</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>幸福二期</t>
+          <t>朱绶青</t>
         </is>
       </c>
       <c r="E184" t="inlineStr"/>
       <c r="F184" t="inlineStr"/>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t>300.0</t>
-        </is>
-      </c>
+      <c r="G184" t="inlineStr"/>
       <c r="H184" t="inlineStr"/>
-      <c r="I184" t="inlineStr">
-        <is>
-          <t>300.0</t>
-        </is>
-      </c>
+      <c r="I184" t="inlineStr"/>
       <c r="J184" t="inlineStr"/>
       <c r="K184" t="inlineStr">
         <is>
@@ -9141,37 +9557,33 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>920100_三协电机</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2002-11-07</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-08-09</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>牛威</t>
+          <t>盛祎</t>
         </is>
       </c>
       <c r="E185" t="inlineStr"/>
-      <c r="F185" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+      <c r="F185" t="inlineStr"/>
       <c r="G185" t="inlineStr"/>
       <c r="H185" t="inlineStr"/>
       <c r="I185" t="inlineStr"/>
@@ -9190,37 +9602,29 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>920100_三协电机</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2002-11-07</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-08-09</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>策星九天</t>
+          <t>深圳市稳正景明创业投资企业(有限合伙)</t>
         </is>
       </c>
       <c r="E186" t="inlineStr"/>
       <c r="F186" t="inlineStr"/>
-      <c r="G186" t="inlineStr">
-        <is>
-          <t>2345.0781</t>
-        </is>
-      </c>
+      <c r="G186" t="inlineStr"/>
       <c r="H186" t="inlineStr"/>
-      <c r="I186" t="inlineStr">
-        <is>
-          <t>2345.0781</t>
-        </is>
-      </c>
+      <c r="I186" t="inlineStr"/>
       <c r="J186" t="inlineStr"/>
       <c r="K186" t="inlineStr">
         <is>
@@ -9241,32 +9645,28 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
+          <t>2016-12-14</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
           <t>2017-10-25</t>
         </is>
       </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>2024-06-30</t>
-        </is>
-      </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>中科星图股份有限公司</t>
+          <t>四方股份</t>
         </is>
       </c>
       <c r="E187" t="inlineStr"/>
-      <c r="F187" t="inlineStr"/>
-      <c r="G187" t="inlineStr">
-        <is>
-          <t>3825.0</t>
-        </is>
-      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>1200.0</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr"/>
       <c r="H187" t="inlineStr"/>
-      <c r="I187" t="inlineStr">
-        <is>
-          <t>3825.0</t>
-        </is>
-      </c>
+      <c r="I187" t="inlineStr"/>
       <c r="J187" t="inlineStr"/>
       <c r="K187" t="inlineStr">
         <is>
@@ -9275,7 +9675,7 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -9287,23 +9687,23 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
+          <t>2016-12-14</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
           <t>2017-10-25</t>
         </is>
       </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>2024-06-30</t>
-        </is>
-      </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>吴功友</t>
+          <t>吴功友(王金林代持)</t>
         </is>
       </c>
       <c r="E188" t="inlineStr"/>
       <c r="F188" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>400.0</t>
         </is>
       </c>
       <c r="G188" t="inlineStr"/>
@@ -9329,32 +9729,24 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
+          <t>2016-12-14</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
           <t>2017-10-25</t>
         </is>
       </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>2024-06-30</t>
-        </is>
-      </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>策星揽月</t>
+          <t>牛威</t>
         </is>
       </c>
       <c r="E189" t="inlineStr"/>
       <c r="F189" t="inlineStr"/>
-      <c r="G189" t="inlineStr">
-        <is>
-          <t>412.5</t>
-        </is>
-      </c>
+      <c r="G189" t="inlineStr"/>
       <c r="H189" t="inlineStr"/>
-      <c r="I189" t="inlineStr">
-        <is>
-          <t>412.5</t>
-        </is>
-      </c>
+      <c r="I189" t="inlineStr"/>
       <c r="J189" t="inlineStr"/>
       <c r="K189" t="inlineStr">
         <is>
@@ -9375,32 +9767,24 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
+          <t>2016-12-14</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
           <t>2017-10-25</t>
         </is>
       </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>2024-06-30</t>
-        </is>
-      </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>幸福一期</t>
+          <t>吴功友</t>
         </is>
       </c>
       <c r="E190" t="inlineStr"/>
       <c r="F190" t="inlineStr"/>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>917.4219</t>
-        </is>
-      </c>
+      <c r="G190" t="inlineStr"/>
       <c r="H190" t="inlineStr"/>
-      <c r="I190" t="inlineStr">
-        <is>
-          <t>917.4219</t>
-        </is>
-      </c>
+      <c r="I190" t="inlineStr"/>
       <c r="J190" t="inlineStr"/>
       <c r="K190" t="inlineStr">
         <is>
@@ -9421,32 +9805,28 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
+          <t>2016-12-14</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
           <t>2017-10-25</t>
         </is>
       </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>2024-06-30</t>
-        </is>
-      </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>策星银河</t>
+          <t>牛威(罗永红代持)</t>
         </is>
       </c>
       <c r="E191" t="inlineStr"/>
-      <c r="F191" t="inlineStr"/>
-      <c r="G191" t="inlineStr">
-        <is>
-          <t>279.0</t>
-        </is>
-      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>400.0</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr"/>
       <c r="H191" t="inlineStr"/>
-      <c r="I191" t="inlineStr">
-        <is>
-          <t>279.0</t>
-        </is>
-      </c>
+      <c r="I191" t="inlineStr"/>
       <c r="J191" t="inlineStr"/>
       <c r="K191" t="inlineStr">
         <is>
@@ -9455,7 +9835,7 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -9477,22 +9857,18 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>策星逐日</t>
+          <t>牛威</t>
         </is>
       </c>
       <c r="E192" t="inlineStr"/>
-      <c r="F192" t="inlineStr"/>
-      <c r="G192" t="inlineStr">
-        <is>
-          <t>171.0</t>
-        </is>
-      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr"/>
       <c r="H192" t="inlineStr"/>
-      <c r="I192" t="inlineStr">
-        <is>
-          <t>171.0</t>
-        </is>
-      </c>
+      <c r="I192" t="inlineStr"/>
       <c r="J192" t="inlineStr"/>
       <c r="K192" t="inlineStr">
         <is>
@@ -9501,7 +9877,7 @@
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -9511,7 +9887,11 @@
           <t>920116_星图测控</t>
         </is>
       </c>
-      <c r="B193" t="inlineStr"/>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
       <c r="C193" t="inlineStr">
         <is>
           <t>2024-06-30</t>
@@ -9519,31 +9899,23 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>中科星图股份有限公司 (认缴→存量)</t>
+          <t>策星揽月</t>
         </is>
       </c>
       <c r="E193" t="inlineStr"/>
       <c r="F193" t="inlineStr"/>
       <c r="G193" t="inlineStr">
         <is>
-          <t>3825.0</t>
-        </is>
-      </c>
-      <c r="H193" t="inlineStr">
-        <is>
-          <t>3825.0</t>
-        </is>
-      </c>
+          <t>412.5</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr"/>
       <c r="I193" t="inlineStr">
         <is>
-          <t>3825.0</t>
-        </is>
-      </c>
-      <c r="J193" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>412.5</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr"/>
       <c r="K193" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -9551,7 +9923,7 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -9561,7 +9933,11 @@
           <t>920116_星图测控</t>
         </is>
       </c>
-      <c r="B194" t="inlineStr"/>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
       <c r="C194" t="inlineStr">
         <is>
           <t>2024-06-30</t>
@@ -9569,7 +9945,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>策星九天 (认缴→存量)</t>
+          <t>策星九天</t>
         </is>
       </c>
       <c r="E194" t="inlineStr"/>
@@ -9579,21 +9955,13 @@
           <t>2345.0781</t>
         </is>
       </c>
-      <c r="H194" t="inlineStr">
+      <c r="H194" t="inlineStr"/>
+      <c r="I194" t="inlineStr">
         <is>
           <t>2345.0781</t>
         </is>
       </c>
-      <c r="I194" t="inlineStr">
-        <is>
-          <t>2345.0781</t>
-        </is>
-      </c>
-      <c r="J194" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+      <c r="J194" t="inlineStr"/>
       <c r="K194" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -9601,7 +9969,7 @@
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -9611,7 +9979,11 @@
           <t>920116_星图测控</t>
         </is>
       </c>
-      <c r="B195" t="inlineStr"/>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
       <c r="C195" t="inlineStr">
         <is>
           <t>2024-06-30</t>
@@ -9619,31 +9991,23 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>幸福一期 (认缴→存量)</t>
+          <t>幸福二期</t>
         </is>
       </c>
       <c r="E195" t="inlineStr"/>
       <c r="F195" t="inlineStr"/>
       <c r="G195" t="inlineStr">
         <is>
-          <t>917.4219</t>
-        </is>
-      </c>
-      <c r="H195" t="inlineStr">
-        <is>
-          <t>917.4219</t>
-        </is>
-      </c>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr"/>
       <c r="I195" t="inlineStr">
         <is>
-          <t>917.4219</t>
-        </is>
-      </c>
-      <c r="J195" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr"/>
       <c r="K195" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -9651,7 +10015,7 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -9661,7 +10025,11 @@
           <t>920116_星图测控</t>
         </is>
       </c>
-      <c r="B196" t="inlineStr"/>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
       <c r="C196" t="inlineStr">
         <is>
           <t>2024-06-30</t>
@@ -9669,31 +10037,23 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>策星揽月 (认缴→存量)</t>
+          <t>幸福一期</t>
         </is>
       </c>
       <c r="E196" t="inlineStr"/>
       <c r="F196" t="inlineStr"/>
       <c r="G196" t="inlineStr">
         <is>
-          <t>412.5</t>
-        </is>
-      </c>
-      <c r="H196" t="inlineStr">
-        <is>
-          <t>412.5</t>
-        </is>
-      </c>
+          <t>917.4219</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr"/>
       <c r="I196" t="inlineStr">
         <is>
-          <t>412.5</t>
-        </is>
-      </c>
-      <c r="J196" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>917.4219</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr"/>
       <c r="K196" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -9701,7 +10061,7 @@
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -9711,7 +10071,11 @@
           <t>920116_星图测控</t>
         </is>
       </c>
-      <c r="B197" t="inlineStr"/>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
       <c r="C197" t="inlineStr">
         <is>
           <t>2024-06-30</t>
@@ -9719,31 +10083,23 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>幸福二期 (认缴→存量)</t>
+          <t>中科星图股份有限公司</t>
         </is>
       </c>
       <c r="E197" t="inlineStr"/>
       <c r="F197" t="inlineStr"/>
       <c r="G197" t="inlineStr">
         <is>
-          <t>300.0</t>
-        </is>
-      </c>
-      <c r="H197" t="inlineStr">
-        <is>
-          <t>300.0</t>
-        </is>
-      </c>
+          <t>3825.0</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr"/>
       <c r="I197" t="inlineStr">
         <is>
-          <t>300.0</t>
-        </is>
-      </c>
-      <c r="J197" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>3825.0</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr"/>
       <c r="K197" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -9751,7 +10107,7 @@
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -9761,7 +10117,11 @@
           <t>920116_星图测控</t>
         </is>
       </c>
-      <c r="B198" t="inlineStr"/>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
       <c r="C198" t="inlineStr">
         <is>
           <t>2024-06-30</t>
@@ -9769,31 +10129,23 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>策星银河 (认缴→存量)</t>
+          <t>策星逐日</t>
         </is>
       </c>
       <c r="E198" t="inlineStr"/>
       <c r="F198" t="inlineStr"/>
       <c r="G198" t="inlineStr">
         <is>
-          <t>279.0</t>
-        </is>
-      </c>
-      <c r="H198" t="inlineStr">
-        <is>
-          <t>279.0</t>
-        </is>
-      </c>
+          <t>171.0</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr"/>
       <c r="I198" t="inlineStr">
         <is>
-          <t>279.0</t>
-        </is>
-      </c>
-      <c r="J198" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>171.0</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr"/>
       <c r="K198" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -9801,7 +10153,7 @@
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -9811,7 +10163,11 @@
           <t>920116_星图测控</t>
         </is>
       </c>
-      <c r="B199" t="inlineStr"/>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
       <c r="C199" t="inlineStr">
         <is>
           <t>2024-06-30</t>
@@ -9819,31 +10175,19 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>策星逐日 (认缴→存量)</t>
+          <t>吴功友</t>
         </is>
       </c>
       <c r="E199" t="inlineStr"/>
-      <c r="F199" t="inlineStr"/>
-      <c r="G199" t="inlineStr">
-        <is>
-          <t>171.0</t>
-        </is>
-      </c>
-      <c r="H199" t="inlineStr">
-        <is>
-          <t>171.0</t>
-        </is>
-      </c>
-      <c r="I199" t="inlineStr">
-        <is>
-          <t>171.0</t>
-        </is>
-      </c>
-      <c r="J199" t="inlineStr">
+      <c r="F199" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
+      <c r="G199" t="inlineStr"/>
+      <c r="H199" t="inlineStr"/>
+      <c r="I199" t="inlineStr"/>
+      <c r="J199" t="inlineStr"/>
       <c r="K199" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -9851,35 +10195,431 @@
       </c>
       <c r="L199" t="inlineStr">
         <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>策星银河</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr"/>
+      <c r="F200" t="inlineStr"/>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr"/>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr"/>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>中科星图股份有限公司 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr"/>
+      <c r="F201" t="inlineStr"/>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>3825.0</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>3825.0</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>3825.0</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
           <t>认购数 vs 存量持股数</t>
         </is>
       </c>
     </row>
-    <row r="201">
-      <c r="A201" s="3" t="inlineStr">
-        <is>
-          <t>认缴流量: 24 条</t>
-        </is>
-      </c>
-    </row>
     <row r="202">
-      <c r="A202" s="3" t="inlineStr">
-        <is>
-          <t>股权存量: 22 条</t>
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr"/>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>策星九天 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr"/>
+      <c r="F202" t="inlineStr"/>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>2345.0781</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>2345.0781</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>2345.0781</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>生成时间: 2026-06-12T14:44:15.775996</t>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr"/>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>幸福一期 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr"/>
+      <c r="F203" t="inlineStr"/>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>917.4219</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>917.4219</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>917.4219</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr"/>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>策星揽月 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr"/>
+      <c r="F204" t="inlineStr"/>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>412.5</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>412.5</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>412.5</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr"/>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>幸福二期 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr"/>
+      <c r="F205" t="inlineStr"/>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr"/>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>策星银河 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr"/>
+      <c r="F206" t="inlineStr"/>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr"/>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>策星逐日 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr"/>
+      <c r="F207" t="inlineStr"/>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>171.0</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>171.0</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>171.0</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="3" t="inlineStr">
+        <is>
+          <t>认缴流量: 24 条</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="3" t="inlineStr">
+        <is>
+          <t>股权存量: 22 条</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>生成时间: 2026-06-12T15:16:10.959499</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A22:L22"/>
+    <mergeCell ref="A30:L30"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/week2_excel/301563_云汉芯城_三表抽取.xlsx
+++ b/outputs/week2_excel/301563_云汉芯城_三表抽取.xlsx
@@ -3197,7 +3197,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>孙国敏</t>
+          <t>张松满</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
@@ -3215,11 +3215,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
+      <c r="L34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3239,7 +3235,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>张松满</t>
+          <t>孙国敏</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
@@ -3257,7 +3253,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3277,11 +3277,15 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
+          <t>深圳市云汉电子有限公司</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
@@ -3293,7 +3297,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3315,15 +3319,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>刘云锋</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>25.0</t>
-        </is>
-      </c>
+      <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
@@ -3335,7 +3335,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3395,7 +3395,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
@@ -3433,7 +3433,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>深圳市云汉电子有限公司</t>
+          <t>刘云锋</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
@@ -3475,7 +3475,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>丰利财富（北京）国际资本管理股份有限公司</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
@@ -3491,7 +3491,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3513,7 +3513,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
+          <t>东方富海（上海）创业投资企业（有限合伙）</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
@@ -3529,7 +3529,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3551,7 +3551,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>镇江红土创业投资有限公司</t>
+          <t>深圳市创新投资集团有限公司</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
@@ -3589,7 +3589,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
+          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
@@ -3605,7 +3605,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3627,7 +3627,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>东方富海（上海）创业投资企业（有限合伙）</t>
+          <t>丰利财富（北京）国际资本管理股份有限公司</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
@@ -3643,7 +3643,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3703,7 +3703,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
@@ -3741,7 +3741,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>深圳市创新投资集团有限公司</t>
+          <t>镇江红土创业投资有限公司</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
@@ -3779,15 +3779,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>丰利财富（北京）国际资本管理股份有限公司</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
@@ -3799,7 +3795,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3821,7 +3817,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>刘云锋</t>
+          <t>深圳市创新投资集团有限公司</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
@@ -3837,7 +3833,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3859,7 +3855,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>昆山红土高新创业投资有限公司</t>
+          <t>刘云锋</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
@@ -3875,7 +3871,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3897,7 +3893,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>镇江红土创业投资有限公司</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
@@ -3913,7 +3909,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3935,7 +3931,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>曾烨</t>
+          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
@@ -3951,7 +3947,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3973,11 +3969,15 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
+          <t>丰利财富（北京）国际资本管理股份有限公司</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
@@ -4011,7 +4011,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>深圳市创新投资集团有限公司</t>
+          <t>曾烨</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
@@ -4027,7 +4027,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4049,7 +4049,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>镇江红土创业投资有限公司</t>
+          <t>昆山红土高新创业投资有限公司</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
@@ -4087,7 +4087,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>曾烨</t>
+          <t>珠海拓域投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
@@ -4103,7 +4103,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>珠海拓域投资合伙企业（有限合伙）</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
@@ -4141,7 +4141,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4201,7 +4201,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
+          <t>夏东</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
@@ -4239,7 +4239,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>刘云锋</t>
+          <t>CASREV FUND</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
@@ -4255,7 +4255,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>CASREV FUND</t>
+          <t>刘云锋</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4315,7 +4315,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>夏东</t>
+          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
@@ -4353,7 +4353,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
@@ -4369,7 +4369,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
+          <t>曾烨</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
@@ -4407,7 +4407,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4429,13 +4429,13 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>CASREV FUND</t>
+          <t>珠海拓域投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>1000.0</t>
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
@@ -4471,13 +4471,13 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
+          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>7412.0</t>
+          <t>1584.0</t>
         </is>
       </c>
       <c r="G67" t="inlineStr"/>
@@ -4513,13 +4513,13 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>夏东</t>
+          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="G68" t="inlineStr"/>
@@ -4555,13 +4555,13 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
+          <t>夏东</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="G69" t="inlineStr"/>
@@ -4597,13 +4597,13 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>珠海拓域投资合伙企业（有限合伙）</t>
+          <t>CASREV FUND</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
-          <t>1000.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="G70" t="inlineStr"/>
@@ -4677,13 +4677,13 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
+          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
-          <t>1584.0</t>
+          <t>7412.0</t>
         </is>
       </c>
       <c r="G72" t="inlineStr"/>
@@ -4757,15 +4757,11 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>火炬电子科技股份有限公司</t>
+          <t>中小企业发展基金（深圳有限合伙）</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>5000.0</t>
-        </is>
-      </c>
+      <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr"/>
@@ -4777,7 +4773,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4799,11 +4795,15 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>中小企业发展基金（深圳有限合伙）</t>
+          <t>火炬电子科技股份有限公司</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
-      <c r="F75" t="inlineStr"/>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>5000.0</t>
+        </is>
+      </c>
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr"/>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4875,15 +4875,11 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>昆山谷捷金属制品有限公司</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr"/>
@@ -4895,7 +4891,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4917,11 +4913,15 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>昆山谷捷金属制品有限公司</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr"/>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr"/>
@@ -4933,7 +4933,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
@@ -5149,7 +5149,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5171,7 +5171,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>上海广弘实业有限公司</t>
         </is>
       </c>
       <c r="E85" t="inlineStr"/>
@@ -5187,7 +5187,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5209,7 +5209,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>上海广弘实业有限公司</t>
+          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
@@ -5285,15 +5285,11 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
+          <t>黄山佳捷股权管理中心（有限合伙）</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>1153.0</t>
-        </is>
-      </c>
+      <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr"/>
@@ -5305,7 +5301,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5369,11 +5365,15 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>黄山佳捷股权管理中心（有限合伙）</t>
+          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
         </is>
       </c>
       <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr"/>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>1153.0</t>
+        </is>
+      </c>
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr"/>
@@ -5385,7 +5385,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5445,11 +5445,15 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
+          <t>黄山佳捷股权管理中心（有限合伙）</t>
         </is>
       </c>
       <c r="E92" t="inlineStr"/>
-      <c r="F92" t="inlineStr"/>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2124.81</t>
+        </is>
+      </c>
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr"/>
@@ -5459,11 +5463,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L92" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
+      <c r="L92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -5559,15 +5559,11 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>黄山佳捷股权管理中心（有限合伙）</t>
+          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2124.81</t>
-        </is>
-      </c>
+      <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr"/>
@@ -5577,7 +5573,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L95" t="inlineStr"/>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -6285,14 +6285,22 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>友升太平洋(美国)投资有限公司</t>
+          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr"/>
-      <c r="G110" t="inlineStr"/>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>1020.0</t>
+        </is>
+      </c>
       <c r="H110" t="inlineStr"/>
-      <c r="I110" t="inlineStr"/>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>1020.0</t>
+        </is>
+      </c>
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr">
         <is>
@@ -6301,7 +6309,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6323,20 +6331,20 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>罗世兵</t>
+          <t>上海泽升贸易有限公司</t>
         </is>
       </c>
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="J111" t="inlineStr"/>
@@ -6369,22 +6377,14 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
+          <t>友升太平洋(美国)投资有限公司</t>
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr"/>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
+      <c r="G112" t="inlineStr"/>
       <c r="H112" t="inlineStr"/>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
+      <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr">
         <is>
@@ -6393,7 +6393,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -6415,22 +6415,14 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>上海泽升贸易有限公司</t>
+          <t>上海市青浦县徐泾乡工业公司</t>
         </is>
       </c>
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr"/>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>8976.0</t>
-        </is>
-      </c>
+      <c r="G113" t="inlineStr"/>
       <c r="H113" t="inlineStr"/>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>8976.0</t>
-        </is>
-      </c>
+      <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr">
         <is>
@@ -6439,7 +6431,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -6461,20 +6453,20 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
+          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr">
         <is>
-          <t>1020.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="H114" t="inlineStr"/>
       <c r="I114" t="inlineStr">
         <is>
-          <t>1020.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="J114" t="inlineStr"/>
@@ -6507,14 +6499,22 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>上海市青浦县徐泾乡工业公司</t>
+          <t>罗世兵</t>
         </is>
       </c>
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr"/>
-      <c r="G115" t="inlineStr"/>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>204.0</t>
+        </is>
+      </c>
       <c r="H115" t="inlineStr"/>
-      <c r="I115" t="inlineStr"/>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>204.0</t>
+        </is>
+      </c>
       <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr">
         <is>
@@ -6523,7 +6523,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6545,22 +6545,26 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr"/>
+          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>1020.0</t>
+        </is>
+      </c>
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
         <is>
-          <t>840.0</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr"/>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>840.0</t>
-        </is>
-      </c>
+          <t>1020.0</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>2040.0</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr">
         <is>
@@ -6569,7 +6573,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -6591,23 +6595,23 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>罗世兵</t>
+          <t>上海泽升贸易有限公司</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>408.0</t>
+          <t>17952.0</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -6641,26 +6645,22 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr">
         <is>
-          <t>1800.0</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>3600.0</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr"/>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
       <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr">
         <is>
@@ -6669,7 +6669,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6691,26 +6691,22 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>上海泽升贸易有限公司</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>8976.0</t>
-        </is>
-      </c>
+          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr">
         <is>
-          <t>8976.0</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>17952.0</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr"/>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr">
         <is>
@@ -6719,7 +6715,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6741,22 +6737,26 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>上海骁墨信息技术服务中心(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr"/>
+          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr">
         <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr"/>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
+          <t>1800.0</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>3600.0</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr">
         <is>
@@ -6765,7 +6765,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -6787,26 +6787,22 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>1020.0</t>
-        </is>
-      </c>
+          <t>上海骁墨信息技术服务中心(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr">
         <is>
-          <t>1020.0</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>2040.0</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr"/>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr">
         <is>
@@ -6815,7 +6811,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6837,22 +6833,26 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr"/>
+          <t>罗世兵</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>204.0</t>
+        </is>
+      </c>
       <c r="F122" t="inlineStr"/>
       <c r="G122" t="inlineStr">
         <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="H122" t="inlineStr"/>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
+          <t>204.0</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>408.0</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
       <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr">
         <is>
@@ -6861,7 +6861,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -6883,30 +6883,22 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>840.0</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>7000.0</t>
-        </is>
-      </c>
+          <t>上海杉创智至创业投资合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr"/>
+      <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr">
         <is>
-          <t>840.0</t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>1680.0</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr"/>
+          <t>59.4667</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>59.4667</t>
+        </is>
+      </c>
       <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr">
         <is>
@@ -6915,7 +6907,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -7083,22 +7075,30 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>深圳市财智创赢私募股权投资企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr"/>
-      <c r="F127" t="inlineStr"/>
+          <t>上海骁墨信息技术服务中心(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>1500.0</t>
+        </is>
+      </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>10.1093</t>
-        </is>
-      </c>
-      <c r="H127" t="inlineStr"/>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>10.1093</t>
-        </is>
-      </c>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
       <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr">
         <is>
@@ -7107,7 +7107,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -7129,30 +7129,22 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>上海骁墨信息技术服务中心(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>1500.0</t>
-        </is>
-      </c>
+          <t>深圳市杉晖创业投资合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr"/>
+      <c r="F128" t="inlineStr"/>
       <c r="G128" t="inlineStr">
         <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr"/>
+          <t>297.3333</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>297.3333</t>
+        </is>
+      </c>
       <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr">
         <is>
@@ -7161,7 +7153,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -7183,20 +7175,20 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>深圳市杉晖创业投资合伙企业(有限合伙)</t>
+          <t>深圳市财智创赢私募股权投资企业(有限合伙)</t>
         </is>
       </c>
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>10.1093</t>
         </is>
       </c>
       <c r="H129" t="inlineStr"/>
       <c r="I129" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>10.1093</t>
         </is>
       </c>
       <c r="J129" t="inlineStr"/>
@@ -7229,20 +7221,20 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>江西赣江新区财投晨源股权投资中心(有限合伙)</t>
+          <t>杭州达晨创程股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr"/>
       <c r="G130" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>51.959</t>
         </is>
       </c>
       <c r="H130" t="inlineStr"/>
       <c r="I130" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>51.959</t>
         </is>
       </c>
       <c r="J130" t="inlineStr"/>
@@ -7275,20 +7267,20 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>上海联炻企业管理中心(有限合伙)</t>
+          <t>江西赣江新区财投晨源股权投资中心(有限合伙)</t>
         </is>
       </c>
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr"/>
       <c r="G131" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="H131" t="inlineStr"/>
       <c r="I131" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="J131" t="inlineStr"/>
@@ -7321,20 +7313,20 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>上海杉创智至创业投资合伙企业(有限合伙)</t>
+          <t>安吉璞颉企业管理合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr"/>
       <c r="G132" t="inlineStr">
         <is>
-          <t>59.4667</t>
+          <t>148.6667</t>
         </is>
       </c>
       <c r="H132" t="inlineStr"/>
       <c r="I132" t="inlineStr">
         <is>
-          <t>59.4667</t>
+          <t>148.6667</t>
         </is>
       </c>
       <c r="J132" t="inlineStr"/>
@@ -7367,22 +7359,30 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr"/>
-      <c r="F133" t="inlineStr"/>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>7000.0</t>
+        </is>
+      </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>29.7333</t>
-        </is>
-      </c>
-      <c r="H133" t="inlineStr"/>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>29.7333</t>
-        </is>
-      </c>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>1680.0</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
       <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr">
         <is>
@@ -7391,7 +7391,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -7413,20 +7413,20 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>安吉璞颉企业管理合伙企业(有限合伙)</t>
+          <t>上海联炻企业管理中心(有限合伙)</t>
         </is>
       </c>
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr">
         <is>
-          <t>148.6667</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="H134" t="inlineStr"/>
       <c r="I134" t="inlineStr">
         <is>
-          <t>148.6667</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="J134" t="inlineStr"/>
@@ -7459,20 +7459,20 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>杭州达晨创程股权投资基金合伙企业(有限合伙)</t>
+          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr"/>
       <c r="G135" t="inlineStr">
         <is>
-          <t>51.959</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="H135" t="inlineStr"/>
       <c r="I135" t="inlineStr">
         <is>
-          <t>51.959</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="J135" t="inlineStr"/>
@@ -8355,7 +8355,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>黄学英</t>
+          <t>高新同华</t>
         </is>
       </c>
       <c r="E153" t="inlineStr"/>
@@ -8393,7 +8393,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>华泰大健康一号</t>
+          <t>周乃鼎</t>
         </is>
       </c>
       <c r="E154" t="inlineStr"/>
@@ -8409,7 +8409,7 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -8431,7 +8431,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>复星惟盈</t>
+          <t>Cheer Rise Consultants Limited</t>
         </is>
       </c>
       <c r="E155" t="inlineStr"/>
@@ -8447,7 +8447,7 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -8503,7 +8503,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>黄学英/刘鸿雁</t>
+          <t>黄学英</t>
         </is>
       </c>
       <c r="E157" t="inlineStr"/>
@@ -8519,7 +8519,7 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -8541,7 +8541,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>周乃鼎</t>
+          <t>周金清</t>
         </is>
       </c>
       <c r="E158" t="inlineStr"/>
@@ -8557,7 +8557,7 @@
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -8579,7 +8579,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>国寿疌泉</t>
+          <t>苏州贤达</t>
         </is>
       </c>
       <c r="E159" t="inlineStr"/>
@@ -8617,7 +8617,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>史建伟</t>
+          <t>国寿疌泉</t>
         </is>
       </c>
       <c r="E160" t="inlineStr"/>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -8655,7 +8655,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>高新同华</t>
+          <t>黄学英/刘鸿雁</t>
         </is>
       </c>
       <c r="E161" t="inlineStr"/>
@@ -8671,7 +8671,7 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -8693,7 +8693,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Cheer Rise Consultants Limited</t>
+          <t>复星惟盈</t>
         </is>
       </c>
       <c r="E162" t="inlineStr"/>
@@ -8709,7 +8709,7 @@
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -8731,7 +8731,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>周金清</t>
+          <t>史建伟</t>
         </is>
       </c>
       <c r="E163" t="inlineStr"/>
@@ -8747,7 +8747,7 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -8769,7 +8769,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>苏州贤达</t>
+          <t>华泰大健康一号</t>
         </is>
       </c>
       <c r="E164" t="inlineStr"/>
@@ -8807,7 +8807,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>深圳中证投资有限责任公司</t>
         </is>
       </c>
       <c r="E165" t="inlineStr"/>
@@ -8845,7 +8845,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>金石智娱股权投资（深圳）合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E166" t="inlineStr"/>
@@ -8883,7 +8883,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>厦门富凯海创投资管理有限责任公司</t>
+          <t>北京岚锋创视网络科技有限公司</t>
         </is>
       </c>
       <c r="E167" t="inlineStr"/>
@@ -8899,7 +8899,7 @@
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -8921,7 +8921,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>香港迅雷有限公司</t>
         </is>
       </c>
       <c r="E168" t="inlineStr"/>
@@ -8937,7 +8937,7 @@
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -8959,7 +8959,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>华金同达（深圳）投资合伙企业（有限合伙）</t>
+          <t>厦门富凯海创投资管理有限责任公司</t>
         </is>
       </c>
       <c r="E169" t="inlineStr"/>
@@ -8997,7 +8997,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>金石智娱股权投资（深圳）合伙企业（有限合伙）</t>
+          <t>华金同达（深圳）投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E170" t="inlineStr"/>
@@ -9035,7 +9035,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>深圳中证投资有限责任公司</t>
+          <t>QM101 Limited</t>
         </is>
       </c>
       <c r="E171" t="inlineStr"/>
@@ -9111,7 +9111,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>EARN ACE LIMITED</t>
         </is>
       </c>
       <c r="E173" t="inlineStr"/>
@@ -9149,7 +9149,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>香港迅雷有限公司</t>
         </is>
       </c>
       <c r="E174" t="inlineStr"/>
@@ -9187,11 +9187,15 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>北京岚锋创视网络科技有限公司</t>
         </is>
       </c>
       <c r="E175" t="inlineStr"/>
-      <c r="F175" t="inlineStr"/>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G175" t="inlineStr"/>
       <c r="H175" t="inlineStr"/>
       <c r="I175" t="inlineStr"/>
@@ -9201,11 +9205,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L175" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
+      <c r="L175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -9225,15 +9225,11 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>QM101 Limited</t>
         </is>
       </c>
       <c r="E176" t="inlineStr"/>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F176" t="inlineStr"/>
       <c r="G176" t="inlineStr"/>
       <c r="H176" t="inlineStr"/>
       <c r="I176" t="inlineStr"/>
@@ -9243,7 +9239,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L176" t="inlineStr"/>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -9263,7 +9263,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>EARN ACE LIMITED</t>
         </is>
       </c>
       <c r="E177" t="inlineStr"/>
@@ -9301,7 +9301,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>汇智同裕（深圳）投资合伙企业（有限合伙）</t>
+          <t>香港迅雷有限公司</t>
         </is>
       </c>
       <c r="E178" t="inlineStr"/>
@@ -9317,7 +9317,7 @@
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -9339,7 +9339,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>北京岚锋创视网络科技有限公司</t>
         </is>
       </c>
       <c r="E179" t="inlineStr"/>
@@ -9377,7 +9377,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>汇智同裕（深圳）投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E180" t="inlineStr"/>
@@ -9393,7 +9393,7 @@
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -9415,7 +9415,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>QM101 Limited</t>
         </is>
       </c>
       <c r="E181" t="inlineStr"/>
@@ -9453,7 +9453,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>EARN ACE LIMITED</t>
         </is>
       </c>
       <c r="E182" t="inlineStr"/>
@@ -9541,7 +9541,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>深圳市稳正景明创业投资企业(有限合伙)</t>
+          <t>朱绶青</t>
         </is>
       </c>
       <c r="E184" t="inlineStr"/>
@@ -9557,7 +9557,7 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -9579,7 +9579,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>盛祎</t>
+          <t>深圳市稳正景明创业投资企业(有限合伙)</t>
         </is>
       </c>
       <c r="E185" t="inlineStr"/>
@@ -9595,7 +9595,7 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -9617,7 +9617,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>朱绶青</t>
+          <t>盛祎</t>
         </is>
       </c>
       <c r="E186" t="inlineStr"/>
@@ -9739,11 +9739,15 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>牛威</t>
+          <t>四方股份</t>
         </is>
       </c>
       <c r="E189" t="inlineStr"/>
-      <c r="F189" t="inlineStr"/>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>1200.0</t>
+        </is>
+      </c>
       <c r="G189" t="inlineStr"/>
       <c r="H189" t="inlineStr"/>
       <c r="I189" t="inlineStr"/>
@@ -9755,7 +9759,7 @@
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -9777,7 +9781,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>吴功友</t>
+          <t>牛威</t>
         </is>
       </c>
       <c r="E190" t="inlineStr"/>
@@ -9815,15 +9819,11 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>四方股份</t>
+          <t>吴功友</t>
         </is>
       </c>
       <c r="E191" t="inlineStr"/>
-      <c r="F191" t="inlineStr">
-        <is>
-          <t>1200.0</t>
-        </is>
-      </c>
+      <c r="F191" t="inlineStr"/>
       <c r="G191" t="inlineStr"/>
       <c r="H191" t="inlineStr"/>
       <c r="I191" t="inlineStr"/>
@@ -9835,7 +9835,7 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -9857,20 +9857,20 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>策星九天</t>
+          <t>幸福二期</t>
         </is>
       </c>
       <c r="E192" t="inlineStr"/>
       <c r="F192" t="inlineStr"/>
       <c r="G192" t="inlineStr">
         <is>
-          <t>2345.0781</t>
+          <t>300.0</t>
         </is>
       </c>
       <c r="H192" t="inlineStr"/>
       <c r="I192" t="inlineStr">
         <is>
-          <t>2345.0781</t>
+          <t>300.0</t>
         </is>
       </c>
       <c r="J192" t="inlineStr"/>
@@ -9903,18 +9903,22 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>牛威</t>
+          <t>策星银河</t>
         </is>
       </c>
       <c r="E193" t="inlineStr"/>
-      <c r="F193" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="G193" t="inlineStr"/>
+      <c r="F193" t="inlineStr"/>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
       <c r="H193" t="inlineStr"/>
-      <c r="I193" t="inlineStr"/>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
       <c r="J193" t="inlineStr"/>
       <c r="K193" t="inlineStr">
         <is>
@@ -9923,7 +9927,7 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -9945,20 +9949,20 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>幸福一期</t>
+          <t>策星逐日</t>
         </is>
       </c>
       <c r="E194" t="inlineStr"/>
       <c r="F194" t="inlineStr"/>
       <c r="G194" t="inlineStr">
         <is>
-          <t>917.4219</t>
+          <t>171.0</t>
         </is>
       </c>
       <c r="H194" t="inlineStr"/>
       <c r="I194" t="inlineStr">
         <is>
-          <t>917.4219</t>
+          <t>171.0</t>
         </is>
       </c>
       <c r="J194" t="inlineStr"/>
@@ -9991,20 +9995,20 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>策星逐日</t>
+          <t>策星揽月</t>
         </is>
       </c>
       <c r="E195" t="inlineStr"/>
       <c r="F195" t="inlineStr"/>
       <c r="G195" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>412.5</t>
         </is>
       </c>
       <c r="H195" t="inlineStr"/>
       <c r="I195" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>412.5</t>
         </is>
       </c>
       <c r="J195" t="inlineStr"/>
@@ -10037,22 +10041,18 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>策星银河</t>
+          <t>牛威</t>
         </is>
       </c>
       <c r="E196" t="inlineStr"/>
-      <c r="F196" t="inlineStr"/>
-      <c r="G196" t="inlineStr">
-        <is>
-          <t>279.0</t>
-        </is>
-      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr"/>
       <c r="H196" t="inlineStr"/>
-      <c r="I196" t="inlineStr">
-        <is>
-          <t>279.0</t>
-        </is>
-      </c>
+      <c r="I196" t="inlineStr"/>
       <c r="J196" t="inlineStr"/>
       <c r="K196" t="inlineStr">
         <is>
@@ -10061,7 +10061,7 @@
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -10083,20 +10083,20 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>中科星图股份有限公司</t>
+          <t>幸福一期</t>
         </is>
       </c>
       <c r="E197" t="inlineStr"/>
       <c r="F197" t="inlineStr"/>
       <c r="G197" t="inlineStr">
         <is>
-          <t>3825.0</t>
+          <t>917.4219</t>
         </is>
       </c>
       <c r="H197" t="inlineStr"/>
       <c r="I197" t="inlineStr">
         <is>
-          <t>3825.0</t>
+          <t>917.4219</t>
         </is>
       </c>
       <c r="J197" t="inlineStr"/>
@@ -10129,20 +10129,20 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>幸福二期</t>
+          <t>策星九天</t>
         </is>
       </c>
       <c r="E198" t="inlineStr"/>
       <c r="F198" t="inlineStr"/>
       <c r="G198" t="inlineStr">
         <is>
-          <t>300.0</t>
+          <t>2345.0781</t>
         </is>
       </c>
       <c r="H198" t="inlineStr"/>
       <c r="I198" t="inlineStr">
         <is>
-          <t>300.0</t>
+          <t>2345.0781</t>
         </is>
       </c>
       <c r="J198" t="inlineStr"/>
@@ -10175,20 +10175,20 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>策星揽月</t>
+          <t>中科星图股份有限公司</t>
         </is>
       </c>
       <c r="E199" t="inlineStr"/>
       <c r="F199" t="inlineStr"/>
       <c r="G199" t="inlineStr">
         <is>
-          <t>412.5</t>
+          <t>3825.0</t>
         </is>
       </c>
       <c r="H199" t="inlineStr"/>
       <c r="I199" t="inlineStr">
         <is>
-          <t>412.5</t>
+          <t>3825.0</t>
         </is>
       </c>
       <c r="J199" t="inlineStr"/>
@@ -10612,7 +10612,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>生成时间: 2026-06-12T16:09:12.626153</t>
+          <t>生成时间: 2026-06-12T16:30:01.063900</t>
         </is>
       </c>
     </row>

--- a/outputs/week2_excel/301563_云汉芯城_三表抽取.xlsx
+++ b/outputs/week2_excel/301563_云汉芯城_三表抽取.xlsx
@@ -2535,7 +2535,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L143"/>
+  <dimension ref="A1:L211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3277,15 +3277,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>深圳市云汉电子有限公司</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>25.0</t>
-        </is>
-      </c>
+      <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
@@ -3297,7 +3293,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3319,7 +3315,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
+          <t>东方富海（上海）创业投资企业（有限合伙）</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
@@ -3357,11 +3353,15 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>刘云锋</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
@@ -3373,7 +3373,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3395,7 +3395,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>东方富海（上海）创业投资企业（有限合伙）</t>
+          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
@@ -3433,7 +3433,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>刘云锋</t>
+          <t>深圳市云汉电子有限公司</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
@@ -3475,7 +3475,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>丰利财富（北京）国际资本管理股份有限公司</t>
+          <t>东方富海（上海）创业投资企业（有限合伙）</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
@@ -3491,7 +3491,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3513,7 +3513,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>东方富海（上海）创业投资企业（有限合伙）</t>
+          <t>深圳市创新投资集团有限公司</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
@@ -3529,7 +3529,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3551,7 +3551,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>昆山红土高新创业投资有限公司</t>
+          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
@@ -3567,7 +3567,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3589,7 +3589,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>深圳市创新投资集团有限公司</t>
+          <t>镇江红土创业投资有限公司</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
@@ -3627,7 +3627,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
+          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
@@ -3643,7 +3643,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3665,7 +3665,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>丰利财富（北京）国际资本管理股份有限公司</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
@@ -3681,7 +3681,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3703,7 +3703,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
@@ -3719,7 +3719,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3741,7 +3741,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>镇江红土创业投资有限公司</t>
+          <t>昆山红土高新创业投资有限公司</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
@@ -3779,7 +3779,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>昆山红土高新创业投资有限公司</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
@@ -3795,7 +3795,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3893,15 +3893,11 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>丰利财富（北京）国际资本管理股份有限公司</t>
+          <t>昆山红土高新创业投资有限公司</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
@@ -3935,11 +3931,15 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>丰利财富（北京）国际资本管理股份有限公司</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
@@ -3951,7 +3951,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3973,7 +3973,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
+          <t>刘云锋</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
@@ -3989,7 +3989,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4049,7 +4049,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>刘云锋</t>
+          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
@@ -4065,7 +4065,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
+          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
@@ -4201,7 +4201,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>夏东</t>
+          <t>CASREV FUND</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4315,7 +4315,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>珠海拓域投资合伙企业（有限合伙）</t>
+          <t>夏东</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
@@ -4353,7 +4353,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
@@ -4369,7 +4369,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>CASREV FUND</t>
+          <t>珠海拓域投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
@@ -4429,13 +4429,13 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>CASREV FUND</t>
+          <t>夏东</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
@@ -4471,15 +4471,11 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
+          <t>火炬电子科技股份有限公司</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>7412.0</t>
-        </is>
-      </c>
+      <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
@@ -4491,7 +4487,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4513,13 +4509,13 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
+          <t>珠海拓域投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>1000.0</t>
         </is>
       </c>
       <c r="G68" t="inlineStr"/>
@@ -4555,13 +4551,13 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>珠海拓域投资合伙企业（有限合伙）</t>
+          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
-          <t>1000.0</t>
+          <t>1584.0</t>
         </is>
       </c>
       <c r="G69" t="inlineStr"/>
@@ -4597,11 +4593,15 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>火炬电子科技股份有限公司</t>
+          <t>CASREV FUND</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr"/>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
@@ -4613,7 +4613,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4635,13 +4635,13 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
+          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
-          <t>1584.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="G71" t="inlineStr"/>
@@ -4677,13 +4677,13 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>夏东</t>
+          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>7412.0</t>
         </is>
       </c>
       <c r="G72" t="inlineStr"/>
@@ -4719,15 +4719,11 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>火炬电子科技股份有限公司</t>
+          <t>厦门西堤股权投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>5000.0</t>
-        </is>
-      </c>
+      <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr"/>
@@ -4739,7 +4735,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4761,11 +4757,15 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>中小企业发展基金（深圳有限合伙）</t>
+          <t>火炬电子科技股份有限公司</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr"/>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>5000.0</t>
+        </is>
+      </c>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr"/>
@@ -4777,7 +4777,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4799,7 +4799,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>厦门西堤股权投资合伙企业（有限合伙）</t>
+          <t>中小企业发展基金（深圳有限合伙）</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
@@ -4875,11 +4875,15 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>昆山谷捷金属制品有限公司</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr"/>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr"/>
@@ -4891,7 +4895,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4917,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
@@ -4951,15 +4955,11 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>昆山谷捷金属制品有限公司</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr"/>
@@ -4971,7 +4971,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>张俊武</t>
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
@@ -5027,7 +5027,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>张俊武</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
@@ -5061,7 +5061,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
@@ -5095,7 +5095,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
+          <t>张俊武</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
@@ -5111,7 +5111,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>上海广弘实业有限公司</t>
+          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
@@ -5171,7 +5171,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>上海广弘实业有限公司</t>
         </is>
       </c>
       <c r="E85" t="inlineStr"/>
@@ -5187,7 +5187,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5209,7 +5209,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>张俊武</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
@@ -5247,7 +5247,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E87" t="inlineStr"/>
@@ -5285,11 +5285,15 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>黄山佳捷股权管理中心（有限合伙）</t>
+          <t>上海广弘实业有限公司</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr"/>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>10377.0</t>
+        </is>
+      </c>
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr"/>
@@ -5301,7 +5305,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5323,15 +5327,11 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
+          <t>黄山佳捷股权管理中心（有限合伙）</t>
         </is>
       </c>
       <c r="E89" t="inlineStr"/>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>1153.0</t>
-        </is>
-      </c>
+      <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr"/>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5365,13 +5365,13 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>上海广弘实业有限公司</t>
+          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
         </is>
       </c>
       <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
-          <t>10377.0</t>
+          <t>1153.0</t>
         </is>
       </c>
       <c r="G90" t="inlineStr"/>
@@ -5407,11 +5407,15 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
+          <t>黄山佳捷股权管理中心（有限合伙）</t>
         </is>
       </c>
       <c r="E91" t="inlineStr"/>
-      <c r="F91" t="inlineStr"/>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2124.81</t>
+        </is>
+      </c>
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr"/>
@@ -5421,11 +5425,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L91" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
+      <c r="L91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -5445,7 +5445,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>上海广弘实业有限公司</t>
+          <t>张俊武</t>
         </is>
       </c>
       <c r="E92" t="inlineStr"/>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
         </is>
       </c>
       <c r="E93" t="inlineStr"/>
@@ -5521,15 +5521,11 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>黄山佳捷股权管理中心（有限合伙）</t>
+          <t>上海广弘实业有限公司</t>
         </is>
       </c>
       <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2124.81</t>
-        </is>
-      </c>
+      <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr"/>
@@ -5539,7 +5535,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L94" t="inlineStr"/>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5559,7 +5559,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>张俊武</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
@@ -5597,7 +5597,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
@@ -5620,30 +5620,42 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>2015-01</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr"/>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr"/>
-      <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr"/>
-      <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>6999.972</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>7000.0</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>-0.028</t>
+        </is>
+      </c>
       <c r="K97" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5651,37 +5663,49 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>2015-01</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr"/>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr"/>
-      <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr"/>
-      <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>2999.988</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>3000.0</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>-0.012</t>
+        </is>
+      </c>
       <c r="K98" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5689,37 +5713,49 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>2015-01</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr"/>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>上海骁墨信息技术服务中心(有限合伙)</t>
         </is>
       </c>
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr"/>
-      <c r="G99" t="inlineStr"/>
-      <c r="H99" t="inlineStr"/>
-      <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>1499.994</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>1500.0</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>-0.006</t>
+        </is>
+      </c>
       <c r="K99" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5727,37 +5763,49 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>2015-01</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr"/>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>厦门富凯海创投资管理有限责任公司</t>
+          <t>深圳市杉晖创业投资合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr"/>
-      <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr"/>
-      <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>297.3333</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>10000.0027</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>10000.0</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>0.0027</t>
+        </is>
+      </c>
       <c r="K100" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5765,37 +5813,49 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>2015-01</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr"/>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>深圳市伊敦传媒投资基金合伙企业（有限合伙）</t>
+          <t>上海联炻企业管理中心(有限合伙)</t>
         </is>
       </c>
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr"/>
-      <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr"/>
-      <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>297.3333</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>10000.0027</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>10000.0</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>0.0027</t>
+        </is>
+      </c>
       <c r="K101" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5803,37 +5863,49 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>2015-01</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr"/>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>安吉璞颉企业管理合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr"/>
-      <c r="G102" t="inlineStr"/>
-      <c r="H102" t="inlineStr"/>
-      <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>148.6667</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>5000.0031</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>5000.0</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>0.0031</t>
+        </is>
+      </c>
       <c r="K102" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5841,37 +5913,49 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>2015-01</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr"/>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>深圳中证投资有限责任公司</t>
+          <t>江西赣江新区财投晨源股权投资中心(有限合伙)</t>
         </is>
       </c>
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr"/>
-      <c r="G103" t="inlineStr"/>
-      <c r="H103" t="inlineStr"/>
-      <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>89.2</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>3000.0012</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>3000.0</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>0.0012</t>
+        </is>
+      </c>
       <c r="K103" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5879,37 +5963,49 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>2015-01</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr"/>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>金石智娱股权投资（深圳）合伙企业（有限合伙）</t>
+          <t>深圳市达晨创程私募股权投资基金企业(有限合伙)</t>
         </is>
       </c>
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr"/>
-      <c r="G104" t="inlineStr"/>
-      <c r="H104" t="inlineStr"/>
-      <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>86.5984</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>2912.5034</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>2912.5</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>0.0034</t>
+        </is>
+      </c>
       <c r="K104" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5917,37 +6013,49 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>2015-01</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr"/>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>华金同达（深圳）投资合伙企业（有限合伙）</t>
+          <t>上海杉创智至创业投资合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr"/>
-      <c r="G105" t="inlineStr"/>
-      <c r="H105" t="inlineStr"/>
-      <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>59.4667</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>2000.0019</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>2000.0</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>0.0019</t>
+        </is>
+      </c>
       <c r="K105" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5955,75 +6063,99 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>2015-07-09</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr"/>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>杭州达晨创程股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E106" t="inlineStr"/>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr"/>
-      <c r="H106" t="inlineStr"/>
-      <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>51.959</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>1747.5007</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>1747.5</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>0.0007</t>
+        </is>
+      </c>
       <c r="K106" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="L106" t="inlineStr"/>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>price×shares vs amount diff=0.0%</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>2015-07-09</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr"/>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr"/>
-      <c r="G107" t="inlineStr"/>
-      <c r="H107" t="inlineStr"/>
-      <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>999.9993</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>-0.0007</t>
+        </is>
+      </c>
       <c r="K107" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -6031,37 +6163,49 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>2015-07-09</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr"/>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>深圳市达晨财智创业投资管理有限公司</t>
         </is>
       </c>
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr"/>
-      <c r="G108" t="inlineStr"/>
-      <c r="H108" t="inlineStr"/>
-      <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>999.9993</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>-0.0007</t>
+        </is>
+      </c>
       <c r="K108" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -6069,37 +6213,49 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>2015-07-09</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr"/>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>深圳市财智创赢私募股权投资企业(有限合伙)</t>
         </is>
       </c>
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr"/>
-      <c r="G109" t="inlineStr"/>
-      <c r="H109" t="inlineStr"/>
-      <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>10.1093</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>339.999</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>340.0</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>-0.001</t>
+        </is>
+      </c>
       <c r="K109" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -6107,29 +6263,29 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>1992-12-04</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2023-03-24</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>上海市青浦县徐泾乡工业公司</t>
         </is>
       </c>
       <c r="E110" t="inlineStr"/>
@@ -6152,29 +6308,37 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>1992-12-04</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2023-03-24</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr"/>
-      <c r="G111" t="inlineStr"/>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="H111" t="inlineStr"/>
-      <c r="I111" t="inlineStr"/>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr">
         <is>
@@ -6183,36 +6347,44 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>1992-12-04</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2023-03-24</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>上海泽升贸易有限公司</t>
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr"/>
-      <c r="G112" t="inlineStr"/>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>8976.0</t>
+        </is>
+      </c>
       <c r="H112" t="inlineStr"/>
-      <c r="I112" t="inlineStr"/>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>8976.0</t>
+        </is>
+      </c>
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr">
         <is>
@@ -6221,36 +6393,44 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>1992-12-04</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2023-03-24</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>汇智同裕（深圳）投资合伙企业（有限合伙）</t>
+          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr"/>
-      <c r="G113" t="inlineStr"/>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>1020.0</t>
+        </is>
+      </c>
       <c r="H113" t="inlineStr"/>
-      <c r="I113" t="inlineStr"/>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>1020.0</t>
+        </is>
+      </c>
       <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr">
         <is>
@@ -6266,22 +6446,22 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>1992-12-04</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2023-03-24</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>友升太平洋(美国)投资有限公司</t>
         </is>
       </c>
       <c r="E114" t="inlineStr"/>
@@ -6304,42 +6484,38 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>920100_三协电机</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr"/>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>1992-12-04</t>
+        </is>
+      </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2023-09-06</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>盛祎等15名自然人</t>
+          <t>罗世兵</t>
         </is>
       </c>
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr">
         <is>
-          <t>321.5</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>1739.315</t>
-        </is>
-      </c>
+          <t>204.0</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr"/>
       <c r="I115" t="inlineStr">
         <is>
-          <t>1723.09</t>
-        </is>
-      </c>
-      <c r="J115" t="inlineStr">
-        <is>
-          <t>16.225</t>
-        </is>
-      </c>
+          <t>204.0</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -6347,36 +6523,44 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>price×shares vs amount diff=0.9%</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>920100_三协电机</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2002-11-07</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2022-08-09</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>深圳市稳正景明创业投资企业(有限合伙)</t>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr"/>
-      <c r="G116" t="inlineStr"/>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
       <c r="H116" t="inlineStr"/>
-      <c r="I116" t="inlineStr"/>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
       <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr">
         <is>
@@ -6392,29 +6576,37 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>920100_三协电机</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2002-11-07</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2022-08-09</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>盛祎</t>
+          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr"/>
-      <c r="G117" t="inlineStr"/>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
       <c r="H117" t="inlineStr"/>
-      <c r="I117" t="inlineStr"/>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
       <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr">
         <is>
@@ -6423,35 +6615,47 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>920100_三协电机</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2002-11-07</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2022-08-09</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>朱绶青</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr"/>
+          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="F118" t="inlineStr"/>
-      <c r="G118" t="inlineStr"/>
-      <c r="H118" t="inlineStr"/>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>3600.0</t>
+        </is>
+      </c>
       <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr">
@@ -6468,33 +6672,37 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2016-12-14</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>四方股份</t>
+          <t>上海骁墨信息技术服务中心(有限合伙)</t>
         </is>
       </c>
       <c r="E119" t="inlineStr"/>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>1200.0</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr"/>
+      <c r="F119" t="inlineStr"/>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
       <c r="H119" t="inlineStr"/>
-      <c r="I119" t="inlineStr"/>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr">
         <is>
@@ -6503,35 +6711,47 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2016-12-14</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>牛威</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr"/>
+          <t>上海泽升贸易有限公司</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>8976.0</t>
+        </is>
+      </c>
       <c r="F120" t="inlineStr"/>
-      <c r="G120" t="inlineStr"/>
-      <c r="H120" t="inlineStr"/>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>8976.0</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>17952.0</t>
+        </is>
+      </c>
       <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr">
@@ -6541,35 +6761,47 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2016-12-14</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>吴功友</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr"/>
+          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>1020.0</t>
+        </is>
+      </c>
       <c r="F121" t="inlineStr"/>
-      <c r="G121" t="inlineStr"/>
-      <c r="H121" t="inlineStr"/>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>1020.0</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>2040.0</t>
+        </is>
+      </c>
       <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr">
@@ -6579,39 +6811,47 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2016-12-14</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>牛威(罗永红代持)</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr"/>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>400.0</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr"/>
-      <c r="H122" t="inlineStr"/>
+          <t>罗世兵</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>204.0</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr"/>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>204.0</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>408.0</t>
+        </is>
+      </c>
       <c r="I122" t="inlineStr"/>
       <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr">
@@ -6628,33 +6868,37 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2016-12-14</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>吴功友(王金林代持)</t>
+          <t>深圳市达晨财智创业投资管理有限公司</t>
         </is>
       </c>
       <c r="E123" t="inlineStr"/>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>400.0</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr"/>
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
       <c r="H123" t="inlineStr"/>
-      <c r="I123" t="inlineStr"/>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
       <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr">
         <is>
@@ -6663,42 +6907,42 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>策星银河</t>
+          <t>江西赣江新区财投晨源股权投资中心(有限合伙)</t>
         </is>
       </c>
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr">
         <is>
-          <t>279.0</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr">
         <is>
-          <t>279.0</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="J124" t="inlineStr"/>
@@ -6716,33 +6960,37 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>牛威</t>
+          <t>上海联炻企业管理中心(有限合伙)</t>
         </is>
       </c>
       <c r="E125" t="inlineStr"/>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr"/>
+      <c r="F125" t="inlineStr"/>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>297.3333</t>
+        </is>
+      </c>
       <c r="H125" t="inlineStr"/>
-      <c r="I125" t="inlineStr"/>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>297.3333</t>
+        </is>
+      </c>
       <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr">
         <is>
@@ -6751,42 +6999,42 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>幸福二期</t>
+          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr">
         <is>
-          <t>300.0</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="H126" t="inlineStr"/>
       <c r="I126" t="inlineStr">
         <is>
-          <t>300.0</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="J126" t="inlineStr"/>
@@ -6804,37 +7052,45 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>策星揽月</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr"/>
-      <c r="F127" t="inlineStr"/>
+          <t>上海骁墨信息技术服务中心(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>1500.0</t>
+        </is>
+      </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>412.5</t>
-        </is>
-      </c>
-      <c r="H127" t="inlineStr"/>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>412.5</t>
-        </is>
-      </c>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
       <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr">
         <is>
@@ -6843,44 +7099,52 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>幸福一期</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr"/>
-      <c r="F128" t="inlineStr"/>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>7000.0</t>
+        </is>
+      </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>917.4219</t>
-        </is>
-      </c>
-      <c r="H128" t="inlineStr"/>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>917.4219</t>
-        </is>
-      </c>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>1680.0</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
       <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr">
         <is>
@@ -6889,42 +7153,42 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>策星九天</t>
+          <t>安吉璞颉企业管理合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr">
         <is>
-          <t>2345.0781</t>
+          <t>148.6667</t>
         </is>
       </c>
       <c r="H129" t="inlineStr"/>
       <c r="I129" t="inlineStr">
         <is>
-          <t>2345.0781</t>
+          <t>148.6667</t>
         </is>
       </c>
       <c r="J129" t="inlineStr"/>
@@ -6942,33 +7206,37 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>吴功友</t>
+          <t>上海杉创智至创业投资合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E130" t="inlineStr"/>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr"/>
+      <c r="F130" t="inlineStr"/>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>59.4667</t>
+        </is>
+      </c>
       <c r="H130" t="inlineStr"/>
-      <c r="I130" t="inlineStr"/>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>59.4667</t>
+        </is>
+      </c>
       <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr">
         <is>
@@ -6977,42 +7245,42 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>策星逐日</t>
+          <t>深圳市财智创赢私募股权投资企业(有限合伙)</t>
         </is>
       </c>
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr"/>
       <c r="G131" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>10.1093</t>
         </is>
       </c>
       <c r="H131" t="inlineStr"/>
       <c r="I131" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>10.1093</t>
         </is>
       </c>
       <c r="J131" t="inlineStr"/>
@@ -7030,37 +7298,45 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>中科星图股份有限公司</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr"/>
-      <c r="F132" t="inlineStr"/>
+          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>3000.0</t>
+        </is>
+      </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>3825.0</t>
-        </is>
-      </c>
-      <c r="H132" t="inlineStr"/>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>3825.0</t>
-        </is>
-      </c>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>720.0</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
       <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr">
         <is>
@@ -7069,49 +7345,45 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr"/>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>中科星图股份有限公司 (认缴→存量)</t>
+          <t>深圳市杉晖创业投资合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr"/>
       <c r="G133" t="inlineStr">
         <is>
-          <t>3825.0</t>
-        </is>
-      </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>3825.0</t>
-        </is>
-      </c>
+          <t>297.3333</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr"/>
       <c r="I133" t="inlineStr">
         <is>
-          <t>3825.0</t>
-        </is>
-      </c>
-      <c r="J133" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>297.3333</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -7119,49 +7391,45 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr"/>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>策星九天 (认缴→存量)</t>
+          <t>深圳市达晨创程私募股权投资基金企业(有限合伙)</t>
         </is>
       </c>
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr">
         <is>
-          <t>2345.0781</t>
-        </is>
-      </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>2345.0781</t>
-        </is>
-      </c>
+          <t>86.5984</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr"/>
       <c r="I134" t="inlineStr">
         <is>
-          <t>2345.0781</t>
-        </is>
-      </c>
-      <c r="J134" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>86.5984</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr"/>
       <c r="K134" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -7169,49 +7437,45 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr"/>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>幸福一期 (认缴→存量)</t>
+          <t>杭州达晨创程股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr"/>
       <c r="G135" t="inlineStr">
         <is>
-          <t>917.4219</t>
-        </is>
-      </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>917.4219</t>
-        </is>
-      </c>
+          <t>51.959</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr"/>
       <c r="I135" t="inlineStr">
         <is>
-          <t>917.4219</t>
-        </is>
-      </c>
-      <c r="J135" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>51.959</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -7219,42 +7483,42 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B136" t="inlineStr"/>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>策星揽月 (认缴→存量)</t>
+          <t>上海泽升贸易有限公司 (认缴→存量)</t>
         </is>
       </c>
       <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr"/>
       <c r="G136" t="inlineStr">
         <is>
-          <t>412.5</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>412.5</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>412.5</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -7276,35 +7540,35 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B137" t="inlineStr"/>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>幸福二期 (认缴→存量)</t>
+          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr"/>
       <c r="G137" t="inlineStr">
         <is>
-          <t>300.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>300.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>300.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -7326,35 +7590,35 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B138" t="inlineStr"/>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>策星银河 (认缴→存量)</t>
+          <t>共青城泽升投资管理合伙企业(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr"/>
       <c r="G138" t="inlineStr">
         <is>
-          <t>279.0</t>
+          <t>1020.0</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>279.0</t>
+          <t>1020.0</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>279.0</t>
+          <t>1020.0</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -7376,35 +7640,35 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B139" t="inlineStr"/>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>策星逐日 (认缴→存量)</t>
+          <t>罗世兵 (认缴→存量)</t>
         </is>
       </c>
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr"/>
       <c r="G139" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -7423,24 +7687,2932 @@
         </is>
       </c>
     </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr"/>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr"/>
+      <c r="F140" t="inlineStr"/>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
     <row r="141">
-      <c r="A141" s="3" t="inlineStr">
-        <is>
-          <t>认缴流量: 24 条</t>
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr"/>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr"/>
+      <c r="F141" t="inlineStr"/>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
         </is>
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="3" t="inlineStr">
-        <is>
-          <t>股权存量: 22 条</t>
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr"/>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>上海骁墨信息技术服务中心(有限合伙) (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr"/>
+      <c r="F142" t="inlineStr"/>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>生成时间: 2026-06-12T17:00:58.765635</t>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr"/>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>2022-12-19</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>深圳市杉晖创业投资合伙企业(有限合伙) (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr"/>
+      <c r="F143" t="inlineStr"/>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>297.3333</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>297.3333</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>297.3333</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr"/>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>2022-12-19</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>上海联炻企业管理中心(有限合伙) (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr"/>
+      <c r="F144" t="inlineStr"/>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>297.3333</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>297.3333</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>297.3333</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr"/>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>2022-12-19</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>安吉璞颉企业管理合伙企业(有限合伙) (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr"/>
+      <c r="F145" t="inlineStr"/>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>148.6667</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>148.6667</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>148.6667</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr"/>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>2022-12-19</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>江西赣江新区财投晨源股权投资中心(有限合伙) (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr"/>
+      <c r="F146" t="inlineStr"/>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>89.2</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>89.2</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>89.2</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr"/>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>2022-12-19</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>深圳市达晨创程私募股权投资基金企业(有限合伙) (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr"/>
+      <c r="F147" t="inlineStr"/>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>86.5984</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>86.5984</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>86.5984</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr"/>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>2022-12-19</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>上海杉创智至创业投资合伙企业(有限合伙) (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr"/>
+      <c r="F148" t="inlineStr"/>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>59.4667</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>59.4667</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>59.4667</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr"/>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>2022-12-19</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>杭州达晨创程股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr"/>
+      <c r="F149" t="inlineStr"/>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>51.959</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>51.959</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>51.959</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr"/>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>2022-12-19</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr"/>
+      <c r="F150" t="inlineStr"/>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr"/>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>2022-12-19</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>深圳市达晨财智创业投资管理有限公司 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr"/>
+      <c r="F151" t="inlineStr"/>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr"/>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>2022-12-19</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>深圳市财智创赢私募股权投资企业(有限合伙) (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr"/>
+      <c r="F152" t="inlineStr"/>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>10.1093</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>10.1093</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>10.1093</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>688758_赛分科技</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>国寿疌泉</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr"/>
+      <c r="F153" t="inlineStr"/>
+      <c r="G153" t="inlineStr"/>
+      <c r="H153" t="inlineStr"/>
+      <c r="I153" t="inlineStr"/>
+      <c r="J153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>688758_赛分科技</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Cheer Rise Consultants Limited</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr"/>
+      <c r="F154" t="inlineStr"/>
+      <c r="G154" t="inlineStr"/>
+      <c r="H154" t="inlineStr"/>
+      <c r="I154" t="inlineStr"/>
+      <c r="J154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>688758_赛分科技</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>复星惟盈</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr"/>
+      <c r="F155" t="inlineStr"/>
+      <c r="G155" t="inlineStr"/>
+      <c r="H155" t="inlineStr"/>
+      <c r="I155" t="inlineStr"/>
+      <c r="J155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>688758_赛分科技</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>苏州贤达</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr"/>
+      <c r="F156" t="inlineStr"/>
+      <c r="G156" t="inlineStr"/>
+      <c r="H156" t="inlineStr"/>
+      <c r="I156" t="inlineStr"/>
+      <c r="J156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>688758_赛分科技</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>黄学英</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr"/>
+      <c r="F157" t="inlineStr"/>
+      <c r="G157" t="inlineStr"/>
+      <c r="H157" t="inlineStr"/>
+      <c r="I157" t="inlineStr"/>
+      <c r="J157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>688758_赛分科技</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>史建伟</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr"/>
+      <c r="F158" t="inlineStr"/>
+      <c r="G158" t="inlineStr"/>
+      <c r="H158" t="inlineStr"/>
+      <c r="I158" t="inlineStr"/>
+      <c r="J158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>688758_赛分科技</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>周金清</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr"/>
+      <c r="F159" t="inlineStr"/>
+      <c r="G159" t="inlineStr"/>
+      <c r="H159" t="inlineStr"/>
+      <c r="I159" t="inlineStr"/>
+      <c r="J159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>688758_赛分科技</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>周乃鼎</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr"/>
+      <c r="F160" t="inlineStr"/>
+      <c r="G160" t="inlineStr"/>
+      <c r="H160" t="inlineStr"/>
+      <c r="I160" t="inlineStr"/>
+      <c r="J160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>688758_赛分科技</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>华泰大健康一号</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr"/>
+      <c r="F161" t="inlineStr"/>
+      <c r="G161" t="inlineStr"/>
+      <c r="H161" t="inlineStr"/>
+      <c r="I161" t="inlineStr"/>
+      <c r="J161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>688758_赛分科技</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>高新同华</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr"/>
+      <c r="F162" t="inlineStr"/>
+      <c r="G162" t="inlineStr"/>
+      <c r="H162" t="inlineStr"/>
+      <c r="I162" t="inlineStr"/>
+      <c r="J162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>688758_赛分科技</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>陆民</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr"/>
+      <c r="F163" t="inlineStr"/>
+      <c r="G163" t="inlineStr"/>
+      <c r="H163" t="inlineStr"/>
+      <c r="I163" t="inlineStr"/>
+      <c r="J163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>688758_赛分科技</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>黄学英/刘鸿雁</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr"/>
+      <c r="F164" t="inlineStr"/>
+      <c r="G164" t="inlineStr"/>
+      <c r="H164" t="inlineStr"/>
+      <c r="I164" t="inlineStr"/>
+      <c r="J164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>EARN ACE LIMITED</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr"/>
+      <c r="F165" t="inlineStr"/>
+      <c r="G165" t="inlineStr"/>
+      <c r="H165" t="inlineStr"/>
+      <c r="I165" t="inlineStr"/>
+      <c r="J165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>深圳中证投资有限责任公司</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr"/>
+      <c r="F166" t="inlineStr"/>
+      <c r="G166" t="inlineStr"/>
+      <c r="H166" t="inlineStr"/>
+      <c r="I166" t="inlineStr"/>
+      <c r="J166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>华金同达（深圳）投资合伙企业（有限合伙）</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr"/>
+      <c r="F167" t="inlineStr"/>
+      <c r="G167" t="inlineStr"/>
+      <c r="H167" t="inlineStr"/>
+      <c r="I167" t="inlineStr"/>
+      <c r="J167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>香港迅雷有限公司</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr"/>
+      <c r="F168" t="inlineStr"/>
+      <c r="G168" t="inlineStr"/>
+      <c r="H168" t="inlineStr"/>
+      <c r="I168" t="inlineStr"/>
+      <c r="J168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>北京岚锋创视网络科技有限公司</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr"/>
+      <c r="F169" t="inlineStr"/>
+      <c r="G169" t="inlineStr"/>
+      <c r="H169" t="inlineStr"/>
+      <c r="I169" t="inlineStr"/>
+      <c r="J169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>深圳市伊敦传媒投资基金合伙企业（有限合伙）</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr"/>
+      <c r="F170" t="inlineStr"/>
+      <c r="G170" t="inlineStr"/>
+      <c r="H170" t="inlineStr"/>
+      <c r="I170" t="inlineStr"/>
+      <c r="J170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>QM101 Limited</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr"/>
+      <c r="F171" t="inlineStr"/>
+      <c r="G171" t="inlineStr"/>
+      <c r="H171" t="inlineStr"/>
+      <c r="I171" t="inlineStr"/>
+      <c r="J171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>金石智娱股权投资（深圳）合伙企业（有限合伙）</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr"/>
+      <c r="F172" t="inlineStr"/>
+      <c r="G172" t="inlineStr"/>
+      <c r="H172" t="inlineStr"/>
+      <c r="I172" t="inlineStr"/>
+      <c r="J172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>厦门富凯海创投资管理有限责任公司</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr"/>
+      <c r="F173" t="inlineStr"/>
+      <c r="G173" t="inlineStr"/>
+      <c r="H173" t="inlineStr"/>
+      <c r="I173" t="inlineStr"/>
+      <c r="J173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>2020-02-26</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>QM101 Limited</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr"/>
+      <c r="F174" t="inlineStr"/>
+      <c r="G174" t="inlineStr"/>
+      <c r="H174" t="inlineStr"/>
+      <c r="I174" t="inlineStr"/>
+      <c r="J174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>2020-02-26</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>EARN ACE LIMITED</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr"/>
+      <c r="F175" t="inlineStr"/>
+      <c r="G175" t="inlineStr"/>
+      <c r="H175" t="inlineStr"/>
+      <c r="I175" t="inlineStr"/>
+      <c r="J175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>2020-02-26</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>香港迅雷有限公司</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr"/>
+      <c r="F176" t="inlineStr"/>
+      <c r="G176" t="inlineStr"/>
+      <c r="H176" t="inlineStr"/>
+      <c r="I176" t="inlineStr"/>
+      <c r="J176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>2020-02-26</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>北京岚锋创视网络科技有限公司</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr"/>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr"/>
+      <c r="H177" t="inlineStr"/>
+      <c r="I177" t="inlineStr"/>
+      <c r="J177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L177" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>2020-02-26</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>2023-03-24</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>汇智同裕（深圳）投资合伙企业（有限合伙）</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr"/>
+      <c r="F178" t="inlineStr"/>
+      <c r="G178" t="inlineStr"/>
+      <c r="H178" t="inlineStr"/>
+      <c r="I178" t="inlineStr"/>
+      <c r="J178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>2020-02-26</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>2023-03-24</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>QM101 Limited</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr"/>
+      <c r="F179" t="inlineStr"/>
+      <c r="G179" t="inlineStr"/>
+      <c r="H179" t="inlineStr"/>
+      <c r="I179" t="inlineStr"/>
+      <c r="J179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>2020-02-26</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>2023-03-24</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>EARN ACE LIMITED</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr"/>
+      <c r="F180" t="inlineStr"/>
+      <c r="G180" t="inlineStr"/>
+      <c r="H180" t="inlineStr"/>
+      <c r="I180" t="inlineStr"/>
+      <c r="J180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>2020-02-26</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>2023-03-24</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>香港迅雷有限公司</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr"/>
+      <c r="F181" t="inlineStr"/>
+      <c r="G181" t="inlineStr"/>
+      <c r="H181" t="inlineStr"/>
+      <c r="I181" t="inlineStr"/>
+      <c r="J181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>2020-02-26</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>2023-03-24</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>北京岚锋创视网络科技有限公司</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr"/>
+      <c r="F182" t="inlineStr"/>
+      <c r="G182" t="inlineStr"/>
+      <c r="H182" t="inlineStr"/>
+      <c r="I182" t="inlineStr"/>
+      <c r="J182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>920100_三协电机</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr"/>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>2023-09-06</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>盛祎等15名自然人</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr"/>
+      <c r="F183" t="inlineStr"/>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>321.5</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>1739.315</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>1723.09</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>16.225</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>price×shares vs amount diff=0.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>920100_三协电机</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>2002-11-07</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>2022-08-09</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>盛祎</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr"/>
+      <c r="F184" t="inlineStr"/>
+      <c r="G184" t="inlineStr"/>
+      <c r="H184" t="inlineStr"/>
+      <c r="I184" t="inlineStr"/>
+      <c r="J184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>920100_三协电机</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>2002-11-07</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>2022-08-09</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>深圳市稳正景明创业投资企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr"/>
+      <c r="F185" t="inlineStr"/>
+      <c r="G185" t="inlineStr"/>
+      <c r="H185" t="inlineStr"/>
+      <c r="I185" t="inlineStr"/>
+      <c r="J185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>920100_三协电机</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>2002-11-07</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>2022-08-09</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>朱绶青</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr"/>
+      <c r="F186" t="inlineStr"/>
+      <c r="G186" t="inlineStr"/>
+      <c r="H186" t="inlineStr"/>
+      <c r="I186" t="inlineStr"/>
+      <c r="J186" t="inlineStr"/>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>2016-12-14</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>四方股份</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr"/>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>1200.0</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr"/>
+      <c r="H187" t="inlineStr"/>
+      <c r="I187" t="inlineStr"/>
+      <c r="J187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>2016-12-14</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>吴功友(王金林代持)</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr"/>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>400.0</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr"/>
+      <c r="H188" t="inlineStr"/>
+      <c r="I188" t="inlineStr"/>
+      <c r="J188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>2016-12-14</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>牛威</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr"/>
+      <c r="F189" t="inlineStr"/>
+      <c r="G189" t="inlineStr"/>
+      <c r="H189" t="inlineStr"/>
+      <c r="I189" t="inlineStr"/>
+      <c r="J189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>2016-12-14</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>吴功友</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr"/>
+      <c r="F190" t="inlineStr"/>
+      <c r="G190" t="inlineStr"/>
+      <c r="H190" t="inlineStr"/>
+      <c r="I190" t="inlineStr"/>
+      <c r="J190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>2016-12-14</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>牛威(罗永红代持)</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr"/>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>400.0</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr"/>
+      <c r="H191" t="inlineStr"/>
+      <c r="I191" t="inlineStr"/>
+      <c r="J191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>策星九天</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr"/>
+      <c r="F192" t="inlineStr"/>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>2345.0781</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr"/>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>2345.0781</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>幸福二期</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr"/>
+      <c r="F193" t="inlineStr"/>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr"/>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr"/>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>策星逐日</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr"/>
+      <c r="F194" t="inlineStr"/>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>171.0</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr"/>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>171.0</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr"/>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>牛威</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr"/>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr"/>
+      <c r="H195" t="inlineStr"/>
+      <c r="I195" t="inlineStr"/>
+      <c r="J195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>吴功友</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr"/>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr"/>
+      <c r="H196" t="inlineStr"/>
+      <c r="I196" t="inlineStr"/>
+      <c r="J196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>中科星图股份有限公司</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr"/>
+      <c r="F197" t="inlineStr"/>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>3825.0</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr"/>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>3825.0</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>幸福一期</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr"/>
+      <c r="F198" t="inlineStr"/>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>917.4219</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr"/>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>917.4219</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>策星揽月</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr"/>
+      <c r="F199" t="inlineStr"/>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>412.5</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr"/>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>412.5</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>策星银河</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr"/>
+      <c r="F200" t="inlineStr"/>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr"/>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr"/>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>中科星图股份有限公司 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr"/>
+      <c r="F201" t="inlineStr"/>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>3825.0</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>3825.0</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>3825.0</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr"/>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>策星九天 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr"/>
+      <c r="F202" t="inlineStr"/>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>2345.0781</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>2345.0781</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>2345.0781</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr"/>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>幸福一期 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr"/>
+      <c r="F203" t="inlineStr"/>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>917.4219</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>917.4219</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>917.4219</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr"/>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>策星揽月 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr"/>
+      <c r="F204" t="inlineStr"/>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>412.5</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>412.5</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>412.5</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr"/>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>幸福二期 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr"/>
+      <c r="F205" t="inlineStr"/>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr"/>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>策星银河 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr"/>
+      <c r="F206" t="inlineStr"/>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr"/>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>策星逐日 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr"/>
+      <c r="F207" t="inlineStr"/>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>171.0</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>171.0</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>171.0</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="3" t="inlineStr">
+        <is>
+          <t>认缴流量: 24 条</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="3" t="inlineStr">
+        <is>
+          <t>股权存量: 22 条</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>生成时间: 2026-06-12T17:05:42.607675</t>
         </is>
       </c>
     </row>
